--- a/research/traditional_assets/database/data/croatia/croatia_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_retail_automotive.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08795261237111252</v>
+        <v>0.08783119766884452</v>
       </c>
       <c r="C2">
-        <v>149.5990102399114</v>
+        <v>148.4332392825089</v>
       </c>
       <c r="D2">
-        <v>124.4990102399114</v>
+        <v>124.8242392825089</v>
       </c>
       <c r="E2">
-        <v>-16.5</v>
+        <v>-15.009</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="G2">
         <v>25.1</v>
@@ -1451,28 +1451,28 @@
         <v>15.16</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07499729999999999</v>
       </c>
       <c r="N2">
-        <v>15.16</v>
+        <v>15.0850027</v>
       </c>
       <c r="O2">
-        <v>2.7288</v>
+        <v>2.715300486</v>
       </c>
       <c r="P2">
-        <v>12.4312</v>
+        <v>12.369702214</v>
       </c>
       <c r="Q2">
-        <v>20.5712</v>
+        <v>20.509702214</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08795261237111252</v>
+        <v>0.08830175522105507</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7166406519669549</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>202.1406103953076</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08783119766884452</v>
+        <v>0.08770978296657654</v>
       </c>
       <c r="C3">
-        <v>148.4332392825089</v>
+        <v>147.2691719686474</v>
       </c>
       <c r="D3">
-        <v>124.8242392825089</v>
+        <v>125.1511719686473</v>
       </c>
       <c r="E3">
-        <v>-15.009</v>
+        <v>-13.518</v>
       </c>
       <c r="F3">
-        <v>1.491</v>
+        <v>2.982</v>
       </c>
       <c r="G3">
         <v>25.1</v>
@@ -1533,28 +1533,28 @@
         <v>15.16</v>
       </c>
       <c r="M3">
-        <v>0.07499729999999999</v>
+        <v>0.1499946</v>
       </c>
       <c r="N3">
-        <v>15.0850027</v>
+        <v>15.0100054</v>
       </c>
       <c r="O3">
-        <v>2.715300486</v>
+        <v>2.701800972</v>
       </c>
       <c r="P3">
-        <v>12.369702214</v>
+        <v>12.308204428</v>
       </c>
       <c r="Q3">
-        <v>20.509702214</v>
+        <v>20.448204428</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08830175522105507</v>
+        <v>0.08865802343528217</v>
       </c>
       <c r="T3">
-        <v>0.7166406519669549</v>
+        <v>0.7226478458814388</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>202.1406103953076</v>
+        <v>101.0703051976538</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08770978296657654</v>
+        <v>0.08758836826430852</v>
       </c>
       <c r="C4">
-        <v>147.2691719686474</v>
+        <v>146.106821719744</v>
       </c>
       <c r="D4">
-        <v>125.1511719686473</v>
+        <v>125.479821719744</v>
       </c>
       <c r="E4">
-        <v>-13.518</v>
+        <v>-12.027</v>
       </c>
       <c r="F4">
-        <v>2.982</v>
+        <v>4.473</v>
       </c>
       <c r="G4">
         <v>25.1</v>
@@ -1615,28 +1615,28 @@
         <v>15.16</v>
       </c>
       <c r="M4">
-        <v>0.1499946</v>
+        <v>0.2249919</v>
       </c>
       <c r="N4">
-        <v>15.0100054</v>
+        <v>14.9350081</v>
       </c>
       <c r="O4">
-        <v>2.701800972</v>
+        <v>2.688301458</v>
       </c>
       <c r="P4">
-        <v>12.308204428</v>
+        <v>12.246706642</v>
       </c>
       <c r="Q4">
-        <v>20.448204428</v>
+        <v>20.386706642</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08865802343528217</v>
+        <v>0.08902163738588507</v>
       </c>
       <c r="T4">
-        <v>0.7226478458814388</v>
+        <v>0.7287788994642626</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.0703051976538</v>
+        <v>67.38020346510253</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08758836826430852</v>
+        <v>0.08746695356204051</v>
       </c>
       <c r="C5">
-        <v>146.106821719744</v>
+        <v>144.9462020985667</v>
       </c>
       <c r="D5">
-        <v>125.479821719744</v>
+        <v>125.8102020985667</v>
       </c>
       <c r="E5">
-        <v>-12.027</v>
+        <v>-10.536</v>
       </c>
       <c r="F5">
-        <v>4.473</v>
+        <v>5.964</v>
       </c>
       <c r="G5">
         <v>25.1</v>
@@ -1697,28 +1697,28 @@
         <v>15.16</v>
       </c>
       <c r="M5">
-        <v>0.2249919</v>
+        <v>0.2999892</v>
       </c>
       <c r="N5">
-        <v>14.9350081</v>
+        <v>14.8600108</v>
       </c>
       <c r="O5">
-        <v>2.688301458</v>
+        <v>2.674801944</v>
       </c>
       <c r="P5">
-        <v>12.246706642</v>
+        <v>12.185208856</v>
       </c>
       <c r="Q5">
-        <v>20.386706642</v>
+        <v>20.325208856</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08902163738588507</v>
+        <v>0.08939282662712554</v>
       </c>
       <c r="T5">
-        <v>0.7287788994642626</v>
+        <v>0.7350376833300618</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.38020346510253</v>
+        <v>50.5351525988269</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08746695356204051</v>
+        <v>0.0873455388597725</v>
       </c>
       <c r="C6">
-        <v>144.9462020985667</v>
+        <v>143.7873268111003</v>
       </c>
       <c r="D6">
-        <v>125.8102020985667</v>
+        <v>126.1423268111003</v>
       </c>
       <c r="E6">
-        <v>-10.536</v>
+        <v>-9.045</v>
       </c>
       <c r="F6">
-        <v>5.964</v>
+        <v>7.455</v>
       </c>
       <c r="G6">
         <v>25.1</v>
@@ -1779,28 +1779,28 @@
         <v>15.16</v>
       </c>
       <c r="M6">
-        <v>0.2999892</v>
+        <v>0.3749865</v>
       </c>
       <c r="N6">
-        <v>14.8600108</v>
+        <v>14.7850135</v>
       </c>
       <c r="O6">
-        <v>2.674801944</v>
+        <v>2.66130243</v>
       </c>
       <c r="P6">
-        <v>12.185208856</v>
+        <v>12.12371107</v>
       </c>
       <c r="Q6">
-        <v>20.325208856</v>
+        <v>20.26371107</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08939282662712554</v>
+        <v>0.0897718303787079</v>
       </c>
       <c r="T6">
-        <v>0.7350376833300618</v>
+        <v>0.7414282310667198</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.5351525988269</v>
+        <v>40.42812207906151</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0873455388597725</v>
+        <v>0.08722412415750451</v>
       </c>
       <c r="C7">
-        <v>143.7873268111003</v>
+        <v>142.6302097084415</v>
       </c>
       <c r="D7">
-        <v>126.1423268111003</v>
+        <v>126.4762097084415</v>
       </c>
       <c r="E7">
-        <v>-9.045</v>
+        <v>-7.554</v>
       </c>
       <c r="F7">
-        <v>7.455</v>
+        <v>8.946</v>
       </c>
       <c r="G7">
         <v>25.1</v>
@@ -1861,28 +1861,28 @@
         <v>15.16</v>
       </c>
       <c r="M7">
-        <v>0.3749865</v>
+        <v>0.4499838</v>
       </c>
       <c r="N7">
-        <v>14.7850135</v>
+        <v>14.7100162</v>
       </c>
       <c r="O7">
-        <v>2.66130243</v>
+        <v>2.647802916</v>
       </c>
       <c r="P7">
-        <v>12.12371107</v>
+        <v>12.062213284</v>
       </c>
       <c r="Q7">
-        <v>20.26371107</v>
+        <v>20.202213284</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0897718303787079</v>
+        <v>0.09015889803989842</v>
       </c>
       <c r="T7">
-        <v>0.7414282310667198</v>
+        <v>0.7479547479041581</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.42812207906151</v>
+        <v>33.69010173255126</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08722412415750451</v>
+        <v>0.08710270945523652</v>
       </c>
       <c r="C8">
-        <v>142.6302097084415</v>
+        <v>141.4748647887247</v>
       </c>
       <c r="D8">
-        <v>126.4762097084415</v>
+        <v>126.8118647887247</v>
       </c>
       <c r="E8">
-        <v>-7.554</v>
+        <v>-6.063000000000001</v>
       </c>
       <c r="F8">
-        <v>8.946</v>
+        <v>10.437</v>
       </c>
       <c r="G8">
         <v>25.1</v>
@@ -1943,28 +1943,28 @@
         <v>15.16</v>
       </c>
       <c r="M8">
-        <v>0.4499838</v>
+        <v>0.5249811</v>
       </c>
       <c r="N8">
-        <v>14.7100162</v>
+        <v>14.6350189</v>
       </c>
       <c r="O8">
-        <v>2.647802916</v>
+        <v>2.634303402</v>
       </c>
       <c r="P8">
-        <v>12.062213284</v>
+        <v>12.000715498</v>
       </c>
       <c r="Q8">
-        <v>20.202213284</v>
+        <v>20.140715498</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09015889803989842</v>
+        <v>0.09055428973681345</v>
       </c>
       <c r="T8">
-        <v>0.7479547479041581</v>
+        <v>0.7546216199424013</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.69010173255126</v>
+        <v>28.87723005647251</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0871027094552365</v>
+        <v>0.08698129475296851</v>
       </c>
       <c r="C9">
-        <v>141.4748647887247</v>
+        <v>140.3213061990784</v>
       </c>
       <c r="D9">
-        <v>126.8118647887247</v>
+        <v>127.1493061990784</v>
       </c>
       <c r="E9">
-        <v>-6.062999999999999</v>
+        <v>-4.572000000000001</v>
       </c>
       <c r="F9">
-        <v>10.437</v>
+        <v>11.928</v>
       </c>
       <c r="G9">
         <v>25.1</v>
@@ -2025,28 +2025,28 @@
         <v>15.16</v>
       </c>
       <c r="M9">
-        <v>0.5249811</v>
+        <v>0.5999783999999999</v>
       </c>
       <c r="N9">
-        <v>14.6350189</v>
+        <v>14.5600216</v>
       </c>
       <c r="O9">
-        <v>2.634303402</v>
+        <v>2.620803888</v>
       </c>
       <c r="P9">
-        <v>12.000715498</v>
+        <v>11.939217712</v>
       </c>
       <c r="Q9">
-        <v>20.140715498</v>
+        <v>20.079217712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09055428973681345</v>
+        <v>0.09095827690540055</v>
       </c>
       <c r="T9">
-        <v>0.7546216199424013</v>
+        <v>0.761433423981476</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.87723005647251</v>
+        <v>25.26757629941345</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08698129475296851</v>
+        <v>0.08685988005070051</v>
       </c>
       <c r="C10">
-        <v>140.3213061990784</v>
+        <v>139.1695482376126</v>
       </c>
       <c r="D10">
-        <v>127.1493061990784</v>
+        <v>127.4885482376126</v>
       </c>
       <c r="E10">
-        <v>-4.572000000000001</v>
+        <v>-3.081000000000001</v>
       </c>
       <c r="F10">
-        <v>11.928</v>
+        <v>13.419</v>
       </c>
       <c r="G10">
         <v>25.1</v>
@@ -2107,28 +2107,28 @@
         <v>15.16</v>
       </c>
       <c r="M10">
-        <v>0.5999783999999999</v>
+        <v>0.6749757</v>
       </c>
       <c r="N10">
-        <v>14.5600216</v>
+        <v>14.4850243</v>
       </c>
       <c r="O10">
-        <v>2.620803888</v>
+        <v>2.607304374</v>
       </c>
       <c r="P10">
-        <v>11.939217712</v>
+        <v>11.877719926</v>
       </c>
       <c r="Q10">
-        <v>20.079217712</v>
+        <v>20.017719926</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09095827690540055</v>
+        <v>0.09137114291285769</v>
       </c>
       <c r="T10">
-        <v>0.761433423981476</v>
+        <v>0.7683949379994313</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.26757629941345</v>
+        <v>22.46006782170084</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08685988005070051</v>
+        <v>0.08673846534843252</v>
       </c>
       <c r="C11">
-        <v>139.1695482376126</v>
+        <v>138.0196053554383</v>
       </c>
       <c r="D11">
-        <v>127.4885482376126</v>
+        <v>127.8296053554383</v>
       </c>
       <c r="E11">
-        <v>-3.081000000000001</v>
+        <v>-1.590000000000002</v>
       </c>
       <c r="F11">
-        <v>13.419</v>
+        <v>14.91</v>
       </c>
       <c r="G11">
         <v>25.1</v>
@@ -2189,28 +2189,28 @@
         <v>15.16</v>
       </c>
       <c r="M11">
-        <v>0.6749757</v>
+        <v>0.7499729999999999</v>
       </c>
       <c r="N11">
-        <v>14.4850243</v>
+        <v>14.410027</v>
       </c>
       <c r="O11">
-        <v>2.607304374</v>
+        <v>2.59380486</v>
       </c>
       <c r="P11">
-        <v>11.877719926</v>
+        <v>11.81622214</v>
       </c>
       <c r="Q11">
-        <v>20.017719926</v>
+        <v>19.95622214</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09137114291285769</v>
+        <v>0.09179318372048056</v>
       </c>
       <c r="T11">
-        <v>0.7683949379994313</v>
+        <v>0.7755111523288968</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.46006782170084</v>
+        <v>20.21406103953076</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08673846534843252</v>
+        <v>0.08661705064616448</v>
       </c>
       <c r="C12">
-        <v>138.0196053554383</v>
+        <v>136.8714921587199</v>
       </c>
       <c r="D12">
-        <v>127.8296053554383</v>
+        <v>128.17249215872</v>
       </c>
       <c r="E12">
-        <v>-1.59</v>
+        <v>-0.0990000000000002</v>
       </c>
       <c r="F12">
-        <v>14.91</v>
+        <v>16.401</v>
       </c>
       <c r="G12">
         <v>25.1</v>
@@ -2271,28 +2271,28 @@
         <v>15.16</v>
       </c>
       <c r="M12">
-        <v>0.749973</v>
+        <v>0.8249702999999999</v>
       </c>
       <c r="N12">
-        <v>14.410027</v>
+        <v>14.3350297</v>
       </c>
       <c r="O12">
-        <v>2.59380486</v>
+        <v>2.580305346</v>
       </c>
       <c r="P12">
-        <v>11.81622214</v>
+        <v>11.754724354</v>
       </c>
       <c r="Q12">
-        <v>19.95622214</v>
+        <v>19.894724354</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09179318372048056</v>
+        <v>0.09222470859119605</v>
       </c>
       <c r="T12">
-        <v>0.7755111523288968</v>
+        <v>0.7827872815871142</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.21406103953075</v>
+        <v>18.37641912684614</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08661705064616448</v>
+        <v>0.08649563594389649</v>
       </c>
       <c r="C13">
-        <v>136.8714921587199</v>
+        <v>135.7252234107597</v>
       </c>
       <c r="D13">
-        <v>128.17249215872</v>
+        <v>128.5172234107597</v>
       </c>
       <c r="E13">
-        <v>-0.0990000000000002</v>
+        <v>1.391999999999999</v>
       </c>
       <c r="F13">
-        <v>16.401</v>
+        <v>17.892</v>
       </c>
       <c r="G13">
         <v>25.1</v>
@@ -2353,28 +2353,28 @@
         <v>15.16</v>
       </c>
       <c r="M13">
-        <v>0.8249702999999999</v>
+        <v>0.8999676</v>
       </c>
       <c r="N13">
-        <v>14.3350297</v>
+        <v>14.2600324</v>
       </c>
       <c r="O13">
-        <v>2.580305346</v>
+        <v>2.566805832</v>
       </c>
       <c r="P13">
-        <v>11.754724354</v>
+        <v>11.693226568</v>
       </c>
       <c r="Q13">
-        <v>19.894724354</v>
+        <v>19.833226568</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09222470859119605</v>
+        <v>0.09266604084533692</v>
       </c>
       <c r="T13">
-        <v>0.7827872815871142</v>
+        <v>0.7902287774193821</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.37641912684614</v>
+        <v>16.84505086627563</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08649563594389649</v>
+        <v>0.0863742212416285</v>
       </c>
       <c r="C14">
-        <v>135.7252234107597</v>
+        <v>134.5808140341174</v>
       </c>
       <c r="D14">
-        <v>128.5172234107597</v>
+        <v>128.8638140341174</v>
       </c>
       <c r="E14">
-        <v>1.391999999999999</v>
+        <v>2.882999999999999</v>
       </c>
       <c r="F14">
-        <v>17.892</v>
+        <v>19.383</v>
       </c>
       <c r="G14">
         <v>25.1</v>
@@ -2435,28 +2435,28 @@
         <v>15.16</v>
       </c>
       <c r="M14">
-        <v>0.8999676</v>
+        <v>0.9749648999999999</v>
       </c>
       <c r="N14">
-        <v>14.2600324</v>
+        <v>14.1850351</v>
       </c>
       <c r="O14">
-        <v>2.566805832</v>
+        <v>2.553306318</v>
       </c>
       <c r="P14">
-        <v>11.693226568</v>
+        <v>11.631728782</v>
       </c>
       <c r="Q14">
-        <v>19.833226568</v>
+        <v>19.771728782</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09266604084533692</v>
+        <v>0.0931175186685385</v>
       </c>
       <c r="T14">
-        <v>0.7902287774193821</v>
+        <v>0.7978413421213575</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.84505086627563</v>
+        <v>15.54927772271597</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0863742212416285</v>
+        <v>0.0862528065393605</v>
       </c>
       <c r="C15">
-        <v>134.5808140341174</v>
+        <v>133.4382791127632</v>
       </c>
       <c r="D15">
-        <v>128.8638140341174</v>
+        <v>129.2122791127632</v>
       </c>
       <c r="E15">
-        <v>2.882999999999999</v>
+        <v>4.374000000000002</v>
       </c>
       <c r="F15">
-        <v>19.383</v>
+        <v>20.874</v>
       </c>
       <c r="G15">
         <v>25.1</v>
@@ -2517,28 +2517,28 @@
         <v>15.16</v>
       </c>
       <c r="M15">
-        <v>0.9749648999999999</v>
+        <v>1.0499622</v>
       </c>
       <c r="N15">
-        <v>14.1850351</v>
+        <v>14.1100378</v>
       </c>
       <c r="O15">
-        <v>2.553306318</v>
+        <v>2.539806804</v>
       </c>
       <c r="P15">
-        <v>11.631728782</v>
+        <v>11.570230996</v>
       </c>
       <c r="Q15">
-        <v>19.771728782</v>
+        <v>19.710230996</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0931175186685385</v>
+        <v>0.09357949597600057</v>
       </c>
       <c r="T15">
-        <v>0.7978413421213575</v>
+        <v>0.8056309432117508</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.54927772271597</v>
+        <v>14.43861502823626</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0862528065393605</v>
+        <v>0.08613139183709248</v>
       </c>
       <c r="C16">
-        <v>133.4382791127632</v>
+        <v>132.2976338942658</v>
       </c>
       <c r="D16">
-        <v>129.2122791127632</v>
+        <v>129.5626338942658</v>
       </c>
       <c r="E16">
-        <v>4.374000000000002</v>
+        <v>5.865000000000002</v>
       </c>
       <c r="F16">
-        <v>20.874</v>
+        <v>22.365</v>
       </c>
       <c r="G16">
         <v>25.1</v>
@@ -2599,28 +2599,28 @@
         <v>15.16</v>
       </c>
       <c r="M16">
-        <v>1.0499622</v>
+        <v>1.1249595</v>
       </c>
       <c r="N16">
-        <v>14.1100378</v>
+        <v>14.0350405</v>
       </c>
       <c r="O16">
-        <v>2.539806804</v>
+        <v>2.52630729</v>
       </c>
       <c r="P16">
-        <v>11.570230996</v>
+        <v>11.50873321</v>
       </c>
       <c r="Q16">
-        <v>19.710230996</v>
+        <v>19.64873321</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09357949597600057</v>
+        <v>0.09405234333775586</v>
       </c>
       <c r="T16">
-        <v>0.8056309432117508</v>
+        <v>0.8136038290336827</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.43861502823626</v>
+        <v>13.4760406930205</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08613139183709248</v>
+        <v>0.08620677713482448</v>
       </c>
       <c r="C17">
-        <v>132.2976338942658</v>
+        <v>130.5888785238962</v>
       </c>
       <c r="D17">
-        <v>129.5626338942658</v>
+        <v>129.3448785238962</v>
       </c>
       <c r="E17">
-        <v>5.864999999999998</v>
+        <v>7.355999999999998</v>
       </c>
       <c r="F17">
-        <v>22.365</v>
+        <v>23.856</v>
       </c>
       <c r="G17">
         <v>25.1</v>
@@ -2681,45 +2681,45 @@
         <v>15.16</v>
       </c>
       <c r="M17">
-        <v>1.1249595</v>
+        <v>1.2357408</v>
       </c>
       <c r="N17">
-        <v>14.0350405</v>
+        <v>13.9242592</v>
       </c>
       <c r="O17">
-        <v>2.52630729</v>
+        <v>2.506366656</v>
       </c>
       <c r="P17">
-        <v>11.50873321</v>
+        <v>11.417892544</v>
       </c>
       <c r="Q17">
-        <v>19.64873321</v>
+        <v>19.557892544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09405234333775586</v>
+        <v>0.09453644897002915</v>
       </c>
       <c r="T17">
-        <v>0.8136038290336827</v>
+        <v>0.8217665454704225</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.47604069302051</v>
+        <v>12.26794486351831</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08620677713482448</v>
+        <v>0.08609766243255648</v>
       </c>
       <c r="C18">
-        <v>130.5888785238962</v>
+        <v>129.4133010820226</v>
       </c>
       <c r="D18">
-        <v>129.3448785238962</v>
+        <v>129.6603010820226</v>
       </c>
       <c r="E18">
-        <v>7.355999999999998</v>
+        <v>8.847000000000001</v>
       </c>
       <c r="F18">
-        <v>23.856</v>
+        <v>25.347</v>
       </c>
       <c r="G18">
         <v>25.1</v>
@@ -2763,28 +2763,28 @@
         <v>15.16</v>
       </c>
       <c r="M18">
-        <v>1.2357408</v>
+        <v>1.3129746</v>
       </c>
       <c r="N18">
-        <v>13.9242592</v>
+        <v>13.8470254</v>
       </c>
       <c r="O18">
-        <v>2.506366656</v>
+        <v>2.492464572</v>
       </c>
       <c r="P18">
-        <v>11.417892544</v>
+        <v>11.354560828</v>
       </c>
       <c r="Q18">
-        <v>19.557892544</v>
+        <v>19.494560828</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09453644897002915</v>
+        <v>0.09503221979826082</v>
       </c>
       <c r="T18">
-        <v>0.8217665454704225</v>
+        <v>0.8301259538694934</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.26794486351831</v>
+        <v>11.54630104801723</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08609766243255648</v>
+        <v>0.08598854773028848</v>
       </c>
       <c r="C19">
-        <v>129.4133010820226</v>
+        <v>128.2392657901865</v>
       </c>
       <c r="D19">
-        <v>129.6603010820226</v>
+        <v>129.9772657901865</v>
       </c>
       <c r="E19">
-        <v>8.847000000000001</v>
+        <v>10.338</v>
       </c>
       <c r="F19">
-        <v>25.347</v>
+        <v>26.838</v>
       </c>
       <c r="G19">
         <v>25.1</v>
@@ -2845,28 +2845,28 @@
         <v>15.16</v>
       </c>
       <c r="M19">
-        <v>1.3129746</v>
+        <v>1.3902084</v>
       </c>
       <c r="N19">
-        <v>13.8470254</v>
+        <v>13.7697916</v>
       </c>
       <c r="O19">
-        <v>2.492464572</v>
+        <v>2.478562488</v>
       </c>
       <c r="P19">
-        <v>11.354560828</v>
+        <v>11.291229112</v>
       </c>
       <c r="Q19">
-        <v>19.494560828</v>
+        <v>19.431229112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09503221979826082</v>
+        <v>0.09554008259791279</v>
       </c>
       <c r="T19">
-        <v>0.8301259538694934</v>
+        <v>0.8386892502782978</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.54630104801723</v>
+        <v>10.90483987868294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08598854773028848</v>
+        <v>0.08587943302802048</v>
       </c>
       <c r="C20">
-        <v>128.2392657901865</v>
+        <v>127.0667839858208</v>
       </c>
       <c r="D20">
-        <v>129.9772657901865</v>
+        <v>130.2957839858208</v>
       </c>
       <c r="E20">
-        <v>10.338</v>
+        <v>11.829</v>
       </c>
       <c r="F20">
-        <v>26.838</v>
+        <v>28.329</v>
       </c>
       <c r="G20">
         <v>25.1</v>
@@ -2927,28 +2927,28 @@
         <v>15.16</v>
       </c>
       <c r="M20">
-        <v>1.3902084</v>
+        <v>1.4674422</v>
       </c>
       <c r="N20">
-        <v>13.7697916</v>
+        <v>13.6925578</v>
       </c>
       <c r="O20">
-        <v>2.478562488</v>
+        <v>2.464660404</v>
       </c>
       <c r="P20">
-        <v>11.291229112</v>
+        <v>11.227897396</v>
       </c>
       <c r="Q20">
-        <v>19.431229112</v>
+        <v>19.367897396</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09554008259791277</v>
+        <v>0.09606048521977836</v>
       </c>
       <c r="T20">
-        <v>0.8386892502782977</v>
+        <v>0.8474639861046034</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.90483987868294</v>
+        <v>10.33090093769962</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08587943302802048</v>
+        <v>0.08577031832575246</v>
       </c>
       <c r="C21">
-        <v>127.0667839858208</v>
+        <v>125.8958671177643</v>
       </c>
       <c r="D21">
-        <v>130.2957839858208</v>
+        <v>130.6158671177643</v>
       </c>
       <c r="E21">
-        <v>11.829</v>
+        <v>13.32</v>
       </c>
       <c r="F21">
-        <v>28.329</v>
+        <v>29.82</v>
       </c>
       <c r="G21">
         <v>25.1</v>
@@ -3009,28 +3009,28 @@
         <v>15.16</v>
       </c>
       <c r="M21">
-        <v>1.4674422</v>
+        <v>1.544676</v>
       </c>
       <c r="N21">
-        <v>13.6925578</v>
+        <v>13.615324</v>
       </c>
       <c r="O21">
-        <v>2.464660404</v>
+        <v>2.45075832</v>
       </c>
       <c r="P21">
-        <v>11.227897396</v>
+        <v>11.16456568</v>
       </c>
       <c r="Q21">
-        <v>19.367897396</v>
+        <v>19.30456568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09606048521977836</v>
+        <v>0.09659389790719058</v>
       </c>
       <c r="T21">
-        <v>0.8474639861046034</v>
+        <v>0.8564580903265667</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.33090093769962</v>
+        <v>9.814355890814644</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08577031832575246</v>
+        <v>0.08595394362348449</v>
       </c>
       <c r="C22">
-        <v>125.8958671177643</v>
+        <v>123.8671103499855</v>
       </c>
       <c r="D22">
-        <v>130.6158671177643</v>
+        <v>130.0781103499855</v>
       </c>
       <c r="E22">
-        <v>13.32</v>
+        <v>14.811</v>
       </c>
       <c r="F22">
-        <v>29.82</v>
+        <v>31.311</v>
       </c>
       <c r="G22">
         <v>25.1</v>
@@ -3091,45 +3091,45 @@
         <v>15.16</v>
       </c>
       <c r="M22">
-        <v>1.544676</v>
+        <v>1.6751385</v>
       </c>
       <c r="N22">
-        <v>13.615324</v>
+        <v>13.4848615</v>
       </c>
       <c r="O22">
-        <v>2.45075832</v>
+        <v>2.42727507</v>
       </c>
       <c r="P22">
-        <v>11.16456568</v>
+        <v>11.05758643</v>
       </c>
       <c r="Q22">
-        <v>19.30456568</v>
+        <v>19.19758643</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09659389790719058</v>
+        <v>0.09714081471327149</v>
       </c>
       <c r="T22">
-        <v>0.8564580903265667</v>
+        <v>0.8656798933895924</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.814355890814644</v>
+        <v>9.049997955392943</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08595394362348449</v>
+        <v>0.08585876892121648</v>
       </c>
       <c r="C23">
-        <v>123.8671103499855</v>
+        <v>122.6542807542947</v>
       </c>
       <c r="D23">
-        <v>130.0781103499855</v>
+        <v>130.3562807542947</v>
       </c>
       <c r="E23">
-        <v>14.811</v>
+        <v>16.302</v>
       </c>
       <c r="F23">
-        <v>31.311</v>
+        <v>32.802</v>
       </c>
       <c r="G23">
         <v>25.1</v>
@@ -3173,28 +3173,28 @@
         <v>15.16</v>
       </c>
       <c r="M23">
-        <v>1.6751385</v>
+        <v>1.754907</v>
       </c>
       <c r="N23">
-        <v>13.4848615</v>
+        <v>13.405093</v>
       </c>
       <c r="O23">
-        <v>2.42727507</v>
+        <v>2.41291674</v>
       </c>
       <c r="P23">
-        <v>11.05758643</v>
+        <v>10.99217626</v>
       </c>
       <c r="Q23">
-        <v>19.19758643</v>
+        <v>19.13217626</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09714081471327149</v>
+        <v>0.0977017550272006</v>
       </c>
       <c r="T23">
-        <v>0.8656798933895924</v>
+        <v>0.8751381529414136</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.049997955392943</v>
+        <v>8.638634411965992</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08585876892121648</v>
+        <v>0.08576359421894848</v>
       </c>
       <c r="C24">
-        <v>122.6542807542947</v>
+        <v>121.4426434361021</v>
       </c>
       <c r="D24">
-        <v>130.3562807542947</v>
+        <v>130.6356434361021</v>
       </c>
       <c r="E24">
-        <v>16.302</v>
+        <v>17.793</v>
       </c>
       <c r="F24">
-        <v>32.802</v>
+        <v>34.293</v>
       </c>
       <c r="G24">
         <v>25.1</v>
@@ -3255,28 +3255,28 @@
         <v>15.16</v>
       </c>
       <c r="M24">
-        <v>1.754907</v>
+        <v>1.8346755</v>
       </c>
       <c r="N24">
-        <v>13.405093</v>
+        <v>13.3253245</v>
       </c>
       <c r="O24">
-        <v>2.41291674</v>
+        <v>2.39855841</v>
       </c>
       <c r="P24">
-        <v>10.99217626</v>
+        <v>10.92676609</v>
       </c>
       <c r="Q24">
-        <v>19.13217626</v>
+        <v>19.06676609</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0977017550272006</v>
+        <v>0.0982772652194136</v>
       </c>
       <c r="T24">
-        <v>0.8751381529414136</v>
+        <v>0.884842081572503</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.638634411965992</v>
+        <v>8.263041611445731</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08576359421894848</v>
+        <v>0.08566841951668047</v>
       </c>
       <c r="C25">
-        <v>121.4426434361021</v>
+        <v>120.2322060772743</v>
       </c>
       <c r="D25">
-        <v>130.6356434361021</v>
+        <v>130.9162060772743</v>
       </c>
       <c r="E25">
-        <v>17.793</v>
+        <v>19.284</v>
       </c>
       <c r="F25">
-        <v>34.293</v>
+        <v>35.784</v>
       </c>
       <c r="G25">
         <v>25.1</v>
@@ -3337,28 +3337,28 @@
         <v>15.16</v>
       </c>
       <c r="M25">
-        <v>1.8346755</v>
+        <v>1.914444</v>
       </c>
       <c r="N25">
-        <v>13.3253245</v>
+        <v>13.245556</v>
       </c>
       <c r="O25">
-        <v>2.39855841</v>
+        <v>2.38420008</v>
       </c>
       <c r="P25">
-        <v>10.92676609</v>
+        <v>10.86135592</v>
       </c>
       <c r="Q25">
-        <v>19.06676609</v>
+        <v>19.00135592</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0982772652194136</v>
+        <v>0.09886792041668482</v>
       </c>
       <c r="T25">
-        <v>0.884842081572503</v>
+        <v>0.8948013767465158</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.263041611445731</v>
+        <v>7.918748210968825</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08566841951668047</v>
+        <v>0.08573724481441246</v>
       </c>
       <c r="C26">
-        <v>120.2322060772743</v>
+        <v>118.5381976048481</v>
       </c>
       <c r="D26">
-        <v>130.9162060772743</v>
+        <v>130.7131976048481</v>
       </c>
       <c r="E26">
-        <v>19.284</v>
+        <v>20.775</v>
       </c>
       <c r="F26">
-        <v>35.784</v>
+        <v>37.275</v>
       </c>
       <c r="G26">
         <v>25.1</v>
@@ -3419,45 +3419,45 @@
         <v>15.16</v>
       </c>
       <c r="M26">
-        <v>1.914444</v>
+        <v>2.0240325</v>
       </c>
       <c r="N26">
-        <v>13.245556</v>
+        <v>13.1359675</v>
       </c>
       <c r="O26">
-        <v>2.38420008</v>
+        <v>2.36447415</v>
       </c>
       <c r="P26">
-        <v>10.86135592</v>
+        <v>10.77149335</v>
       </c>
       <c r="Q26">
-        <v>19.00135592</v>
+        <v>18.91149335</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09886792041668482</v>
+        <v>0.09947432641921661</v>
       </c>
       <c r="T26">
-        <v>0.8948013767465156</v>
+        <v>0.9050262531251687</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.18</v>
       </c>
       <c r="W26">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.918748210968825</v>
+        <v>7.489998307833496</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08573724481441246</v>
+        <v>0.08564863011214446</v>
       </c>
       <c r="C27">
-        <v>118.5381976048481</v>
+        <v>117.3086940737666</v>
       </c>
       <c r="D27">
-        <v>130.7131976048481</v>
+        <v>130.9746940737666</v>
       </c>
       <c r="E27">
-        <v>20.775</v>
+        <v>22.266</v>
       </c>
       <c r="F27">
-        <v>37.275</v>
+        <v>38.766</v>
       </c>
       <c r="G27">
         <v>25.1</v>
@@ -3501,28 +3501,28 @@
         <v>15.16</v>
       </c>
       <c r="M27">
-        <v>2.0240325</v>
+        <v>2.1049938</v>
       </c>
       <c r="N27">
-        <v>13.1359675</v>
+        <v>13.0550062</v>
       </c>
       <c r="O27">
-        <v>2.36447415</v>
+        <v>2.349901116</v>
       </c>
       <c r="P27">
-        <v>10.77149335</v>
+        <v>10.705105084</v>
       </c>
       <c r="Q27">
-        <v>18.91149335</v>
+        <v>18.845105084</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09947432641921661</v>
+        <v>0.1000971217731682</v>
       </c>
       <c r="T27">
-        <v>0.9050262531251687</v>
+        <v>0.9155274775140556</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.489998307833496</v>
+        <v>7.201921449839901</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08564863011214446</v>
+        <v>0.08556001540987646</v>
       </c>
       <c r="C28">
-        <v>117.3086940737666</v>
+        <v>116.0802389062199</v>
       </c>
       <c r="D28">
-        <v>130.9746940737666</v>
+        <v>131.2372389062199</v>
       </c>
       <c r="E28">
-        <v>22.266</v>
+        <v>23.757</v>
       </c>
       <c r="F28">
-        <v>38.766</v>
+        <v>40.257</v>
       </c>
       <c r="G28">
         <v>25.1</v>
@@ -3583,28 +3583,28 @@
         <v>15.16</v>
       </c>
       <c r="M28">
-        <v>2.1049938</v>
+        <v>2.1859551</v>
       </c>
       <c r="N28">
-        <v>13.0550062</v>
+        <v>12.9740449</v>
       </c>
       <c r="O28">
-        <v>2.349901116</v>
+        <v>2.335328082</v>
       </c>
       <c r="P28">
-        <v>10.705105084</v>
+        <v>10.638716818</v>
       </c>
       <c r="Q28">
-        <v>18.845105084</v>
+        <v>18.778716818</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1000971217731682</v>
+        <v>0.1007369800135294</v>
       </c>
       <c r="T28">
-        <v>0.9155274775140556</v>
+        <v>0.9263164066807202</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.201921449839901</v>
+        <v>6.935183618364349</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08556001540987646</v>
+        <v>0.08547140070760845</v>
       </c>
       <c r="C29">
-        <v>116.0802389062199</v>
+        <v>114.8528384193504</v>
       </c>
       <c r="D29">
-        <v>131.2372389062199</v>
+        <v>131.5008384193505</v>
       </c>
       <c r="E29">
-        <v>23.757</v>
+        <v>25.248</v>
       </c>
       <c r="F29">
-        <v>40.257</v>
+        <v>41.748</v>
       </c>
       <c r="G29">
         <v>25.1</v>
@@ -3665,28 +3665,28 @@
         <v>15.16</v>
       </c>
       <c r="M29">
-        <v>2.1859551</v>
+        <v>2.2669164</v>
       </c>
       <c r="N29">
-        <v>12.9740449</v>
+        <v>12.8930836</v>
       </c>
       <c r="O29">
-        <v>2.335328082</v>
+        <v>2.320755048</v>
       </c>
       <c r="P29">
-        <v>10.638716818</v>
+        <v>10.572328552</v>
       </c>
       <c r="Q29">
-        <v>18.778716818</v>
+        <v>18.712328552</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1007369800135294</v>
+        <v>0.1013946120939006</v>
       </c>
       <c r="T29">
-        <v>0.9263164066807202</v>
+        <v>0.9374050283242368</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.935183618364349</v>
+        <v>6.687498489137049</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08547140070760845</v>
+        <v>0.08538278600534045</v>
       </c>
       <c r="C30">
-        <v>114.8528384193504</v>
+        <v>113.6264989811568</v>
       </c>
       <c r="D30">
-        <v>131.5008384193505</v>
+        <v>131.7654989811568</v>
       </c>
       <c r="E30">
-        <v>25.248</v>
+        <v>26.739</v>
       </c>
       <c r="F30">
-        <v>41.748</v>
+        <v>43.239</v>
       </c>
       <c r="G30">
         <v>25.1</v>
@@ -3747,28 +3747,28 @@
         <v>15.16</v>
       </c>
       <c r="M30">
-        <v>2.2669164</v>
+        <v>2.3478777</v>
       </c>
       <c r="N30">
-        <v>12.8930836</v>
+        <v>12.8121223</v>
       </c>
       <c r="O30">
-        <v>2.320755048</v>
+        <v>2.306182014</v>
       </c>
       <c r="P30">
-        <v>10.572328552</v>
+        <v>10.505940286</v>
       </c>
       <c r="Q30">
-        <v>18.712328552</v>
+        <v>18.645940286</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1013946120939006</v>
+        <v>0.1020707690216063</v>
       </c>
       <c r="T30">
-        <v>0.9374050283242368</v>
+        <v>0.9488060055070071</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.687498489137049</v>
+        <v>6.45689509295991</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08538278600534045</v>
+        <v>0.08529417130307244</v>
       </c>
       <c r="C31">
-        <v>113.6264989811568</v>
+        <v>112.4012270110062</v>
       </c>
       <c r="D31">
-        <v>131.7654989811568</v>
+        <v>132.0312270110062</v>
       </c>
       <c r="E31">
-        <v>26.739</v>
+        <v>28.23</v>
       </c>
       <c r="F31">
-        <v>43.239</v>
+        <v>44.73</v>
       </c>
       <c r="G31">
         <v>25.1</v>
@@ -3829,28 +3829,28 @@
         <v>15.16</v>
       </c>
       <c r="M31">
-        <v>2.3478777</v>
+        <v>2.428839</v>
       </c>
       <c r="N31">
-        <v>12.8121223</v>
+        <v>12.731161</v>
       </c>
       <c r="O31">
-        <v>2.306182014</v>
+        <v>2.29160898</v>
       </c>
       <c r="P31">
-        <v>10.505940286</v>
+        <v>10.43955202</v>
       </c>
       <c r="Q31">
-        <v>18.645940286</v>
+        <v>18.57955202</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1020707690216063</v>
+        <v>0.1027662447186749</v>
       </c>
       <c r="T31">
-        <v>0.9488060055070071</v>
+        <v>0.9605327248949995</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.456895092959911</v>
+        <v>6.241665256527913</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08529417130307244</v>
+        <v>0.08545975660080445</v>
       </c>
       <c r="C32">
-        <v>112.4012270110062</v>
+        <v>110.4145545310265</v>
       </c>
       <c r="D32">
-        <v>132.0312270110062</v>
+        <v>131.5355545310265</v>
       </c>
       <c r="E32">
-        <v>28.23</v>
+        <v>29.721</v>
       </c>
       <c r="F32">
-        <v>44.73</v>
+        <v>46.221</v>
       </c>
       <c r="G32">
         <v>25.1</v>
@@ -3911,45 +3911,45 @@
         <v>15.16</v>
       </c>
       <c r="M32">
-        <v>2.428839</v>
+        <v>2.5560213</v>
       </c>
       <c r="N32">
-        <v>12.731161</v>
+        <v>12.6039787</v>
       </c>
       <c r="O32">
-        <v>2.29160898</v>
+        <v>2.268716166</v>
       </c>
       <c r="P32">
-        <v>10.43955202</v>
+        <v>10.335262534</v>
       </c>
       <c r="Q32">
-        <v>18.57955202</v>
+        <v>18.475262534</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1027662447186749</v>
+        <v>0.1034818791316006</v>
       </c>
       <c r="T32">
-        <v>0.9605327248949995</v>
+        <v>0.9725993491927889</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.18</v>
       </c>
       <c r="W32">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.241665256527913</v>
+        <v>5.931092984240782</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08545975660080445</v>
+        <v>0.08537934189853645</v>
       </c>
       <c r="C33">
-        <v>110.4145545310265</v>
+        <v>109.1638068105123</v>
       </c>
       <c r="D33">
-        <v>131.5355545310265</v>
+        <v>131.7758068105123</v>
       </c>
       <c r="E33">
-        <v>29.721</v>
+        <v>31.212</v>
       </c>
       <c r="F33">
-        <v>46.221</v>
+        <v>47.712</v>
       </c>
       <c r="G33">
         <v>25.1</v>
@@ -3993,28 +3993,28 @@
         <v>15.16</v>
       </c>
       <c r="M33">
-        <v>2.5560213</v>
+        <v>2.6384736</v>
       </c>
       <c r="N33">
-        <v>12.6039787</v>
+        <v>12.5215264</v>
       </c>
       <c r="O33">
-        <v>2.268716166</v>
+        <v>2.253874752</v>
       </c>
       <c r="P33">
-        <v>10.335262534</v>
+        <v>10.267651648</v>
       </c>
       <c r="Q33">
-        <v>18.475262534</v>
+        <v>18.407651648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1034818791316006</v>
+        <v>0.1042185616154948</v>
       </c>
       <c r="T33">
-        <v>0.9725993491927889</v>
+        <v>0.9850208742052191</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.931092984240782</v>
+        <v>5.745746328483257</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08537934189853645</v>
+        <v>0.08529892719626844</v>
       </c>
       <c r="C34">
-        <v>109.1638068105123</v>
+        <v>107.9139383470134</v>
       </c>
       <c r="D34">
-        <v>131.7758068105123</v>
+        <v>132.0169383470134</v>
       </c>
       <c r="E34">
-        <v>31.212</v>
+        <v>32.703</v>
       </c>
       <c r="F34">
-        <v>47.712</v>
+        <v>49.203</v>
       </c>
       <c r="G34">
         <v>25.1</v>
@@ -4075,28 +4075,28 @@
         <v>15.16</v>
       </c>
       <c r="M34">
-        <v>2.6384736</v>
+        <v>2.7209259</v>
       </c>
       <c r="N34">
-        <v>12.5215264</v>
+        <v>12.4390741</v>
       </c>
       <c r="O34">
-        <v>2.253874752</v>
+        <v>2.239033338</v>
       </c>
       <c r="P34">
-        <v>10.267651648</v>
+        <v>10.200040762</v>
       </c>
       <c r="Q34">
-        <v>18.407651648</v>
+        <v>18.340040762</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1042185616154948</v>
+        <v>0.1049772346212962</v>
       </c>
       <c r="T34">
-        <v>0.9850208742052191</v>
+        <v>0.9978131910090652</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.745746328483257</v>
+        <v>5.571632803377702</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08529892719626844</v>
+        <v>0.08521851249400045</v>
       </c>
       <c r="C35">
-        <v>107.9139383470134</v>
+        <v>106.6649539761354</v>
       </c>
       <c r="D35">
-        <v>132.0169383470134</v>
+        <v>132.2589539761354</v>
       </c>
       <c r="E35">
-        <v>32.703</v>
+        <v>34.194</v>
       </c>
       <c r="F35">
-        <v>49.203</v>
+        <v>50.694</v>
       </c>
       <c r="G35">
         <v>25.1</v>
@@ -4157,28 +4157,28 @@
         <v>15.16</v>
       </c>
       <c r="M35">
-        <v>2.7209259</v>
+        <v>2.8033782</v>
       </c>
       <c r="N35">
-        <v>12.4390741</v>
+        <v>12.3566218</v>
       </c>
       <c r="O35">
-        <v>2.239033338</v>
+        <v>2.224191924</v>
       </c>
       <c r="P35">
-        <v>10.200040762</v>
+        <v>10.132429876</v>
       </c>
       <c r="Q35">
-        <v>18.340040762</v>
+        <v>18.272429876</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1049772346212962</v>
+        <v>0.1057588977181825</v>
       </c>
       <c r="T35">
-        <v>0.9978131910090652</v>
+        <v>1.010993153776664</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.571632803377702</v>
+        <v>5.407761250337182</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08521851249400045</v>
+        <v>0.08513809779173243</v>
       </c>
       <c r="C36">
-        <v>106.6649539761354</v>
+        <v>105.4168585690076</v>
       </c>
       <c r="D36">
-        <v>132.2589539761354</v>
+        <v>132.5018585690076</v>
       </c>
       <c r="E36">
-        <v>34.194</v>
+        <v>35.685</v>
       </c>
       <c r="F36">
-        <v>50.694</v>
+        <v>52.185</v>
       </c>
       <c r="G36">
         <v>25.1</v>
@@ -4239,28 +4239,28 @@
         <v>15.16</v>
       </c>
       <c r="M36">
-        <v>2.8033782</v>
+        <v>2.8858305</v>
       </c>
       <c r="N36">
-        <v>12.3566218</v>
+        <v>12.2741695</v>
       </c>
       <c r="O36">
-        <v>2.224191924</v>
+        <v>2.20935051</v>
       </c>
       <c r="P36">
-        <v>10.132429876</v>
+        <v>10.06481899</v>
       </c>
       <c r="Q36">
-        <v>18.272429876</v>
+        <v>18.20481899</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1057588977181825</v>
+        <v>0.1065646119872807</v>
       </c>
       <c r="T36">
-        <v>1.010993153776664</v>
+        <v>1.024578653860189</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.407761250337182</v>
+        <v>5.253253786041833</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08513809779173243</v>
+        <v>0.08505768308946443</v>
       </c>
       <c r="C37">
-        <v>105.4168585690076</v>
+        <v>104.16965703261</v>
       </c>
       <c r="D37">
-        <v>132.5018585690076</v>
+        <v>132.74565703261</v>
       </c>
       <c r="E37">
-        <v>35.685</v>
+        <v>37.176</v>
       </c>
       <c r="F37">
-        <v>52.185</v>
+        <v>53.676</v>
       </c>
       <c r="G37">
         <v>25.1</v>
@@ -4321,28 +4321,28 @@
         <v>15.16</v>
       </c>
       <c r="M37">
-        <v>2.8858305</v>
+        <v>2.9682828</v>
       </c>
       <c r="N37">
-        <v>12.2741695</v>
+        <v>12.1917172</v>
       </c>
       <c r="O37">
-        <v>2.20935051</v>
+        <v>2.194509096</v>
       </c>
       <c r="P37">
-        <v>10.06481899</v>
+        <v>9.997208103999998</v>
       </c>
       <c r="Q37">
-        <v>18.20481899</v>
+        <v>18.137208104</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1065646119872807</v>
+        <v>0.1073955048272882</v>
       </c>
       <c r="T37">
-        <v>1.024578653860189</v>
+        <v>1.038588700821324</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.253253786041833</v>
+        <v>5.107330069762894</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08505768308946444</v>
+        <v>0.08497726838719644</v>
       </c>
       <c r="C38">
-        <v>104.16965703261</v>
+        <v>102.9233543101042</v>
       </c>
       <c r="D38">
-        <v>132.74565703261</v>
+        <v>132.9903543101042</v>
       </c>
       <c r="E38">
-        <v>37.17599999999999</v>
+        <v>38.66699999999999</v>
       </c>
       <c r="F38">
-        <v>53.67599999999999</v>
+        <v>55.16699999999999</v>
       </c>
       <c r="G38">
         <v>25.1</v>
@@ -4403,28 +4403,28 @@
         <v>15.16</v>
       </c>
       <c r="M38">
-        <v>2.9682828</v>
+        <v>3.0507351</v>
       </c>
       <c r="N38">
-        <v>12.1917172</v>
+        <v>12.1092649</v>
       </c>
       <c r="O38">
-        <v>2.194509096</v>
+        <v>2.179667682</v>
       </c>
       <c r="P38">
-        <v>9.997208103999998</v>
+        <v>9.929597218</v>
       </c>
       <c r="Q38">
-        <v>18.137208104</v>
+        <v>18.069597218</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1073955048272882</v>
+        <v>0.1082527752177721</v>
       </c>
       <c r="T38">
-        <v>1.038588700821324</v>
+        <v>1.053043511178051</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.107330069762894</v>
+        <v>4.969294121931465</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08497726838719644</v>
+        <v>0.08489685368492844</v>
       </c>
       <c r="C39">
-        <v>102.9233543101042</v>
+        <v>101.6779553811667</v>
       </c>
       <c r="D39">
-        <v>132.9903543101042</v>
+        <v>133.2359553811667</v>
       </c>
       <c r="E39">
-        <v>38.66699999999999</v>
+        <v>40.158</v>
       </c>
       <c r="F39">
-        <v>55.16699999999999</v>
+        <v>56.658</v>
       </c>
       <c r="G39">
         <v>25.1</v>
@@ -4485,28 +4485,28 @@
         <v>15.16</v>
       </c>
       <c r="M39">
-        <v>3.0507351</v>
+        <v>3.1331874</v>
       </c>
       <c r="N39">
-        <v>12.1092649</v>
+        <v>12.0268126</v>
       </c>
       <c r="O39">
-        <v>2.179667682</v>
+        <v>2.164826268</v>
       </c>
       <c r="P39">
-        <v>9.929597218</v>
+        <v>9.861986332000001</v>
       </c>
       <c r="Q39">
-        <v>18.069597218</v>
+        <v>18.001986332</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1082527752177721</v>
+        <v>0.1091376994918201</v>
       </c>
       <c r="T39">
-        <v>1.053043511178051</v>
+        <v>1.067964605739834</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.969294121931465</v>
+        <v>4.8385232239859</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08489685368492844</v>
+        <v>0.08481643898266042</v>
       </c>
       <c r="C40">
-        <v>101.6779553811667</v>
+        <v>100.4334652623273</v>
       </c>
       <c r="D40">
-        <v>133.2359553811667</v>
+        <v>133.4824652623273</v>
       </c>
       <c r="E40">
-        <v>40.158</v>
+        <v>41.649</v>
       </c>
       <c r="F40">
-        <v>56.658</v>
+        <v>58.149</v>
       </c>
       <c r="G40">
         <v>25.1</v>
@@ -4567,28 +4567,28 @@
         <v>15.16</v>
       </c>
       <c r="M40">
-        <v>3.1331874</v>
+        <v>3.2156397</v>
       </c>
       <c r="N40">
-        <v>12.0268126</v>
+        <v>11.9443603</v>
       </c>
       <c r="O40">
-        <v>2.164826268</v>
+        <v>2.149984854</v>
       </c>
       <c r="P40">
-        <v>9.861986332000001</v>
+        <v>9.794375446</v>
       </c>
       <c r="Q40">
-        <v>18.001986332</v>
+        <v>17.934375446</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1091376994918201</v>
+        <v>0.1100516376764925</v>
       </c>
       <c r="T40">
-        <v>1.067964605739834</v>
+        <v>1.083374916516756</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.8385232239859</v>
+        <v>4.71445852593498</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08481643898266042</v>
+        <v>0.08473602428039241</v>
       </c>
       <c r="C41">
-        <v>100.4334652623273</v>
+        <v>99.1898890073105</v>
       </c>
       <c r="D41">
-        <v>133.4824652623273</v>
+        <v>133.7298890073105</v>
       </c>
       <c r="E41">
-        <v>41.649</v>
+        <v>43.14</v>
       </c>
       <c r="F41">
-        <v>58.149</v>
+        <v>59.64</v>
       </c>
       <c r="G41">
         <v>25.1</v>
@@ -4649,28 +4649,28 @@
         <v>15.16</v>
       </c>
       <c r="M41">
-        <v>3.2156397</v>
+        <v>3.298092</v>
       </c>
       <c r="N41">
-        <v>11.9443603</v>
+        <v>11.861908</v>
       </c>
       <c r="O41">
-        <v>2.149984854</v>
+        <v>2.13514344</v>
       </c>
       <c r="P41">
-        <v>9.794375446</v>
+        <v>9.726764559999999</v>
       </c>
       <c r="Q41">
-        <v>17.934375446</v>
+        <v>17.86676456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1100516376764925</v>
+        <v>0.1109960404673207</v>
       </c>
       <c r="T41">
-        <v>1.083374916516756</v>
+        <v>1.099298904319577</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.71445852593498</v>
+        <v>4.596597062786605</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08473602428039241</v>
+        <v>0.08549610957812444</v>
       </c>
       <c r="C42">
-        <v>99.1898890073105</v>
+        <v>95.39623127168406</v>
       </c>
       <c r="D42">
-        <v>133.7298890073105</v>
+        <v>131.4272312716841</v>
       </c>
       <c r="E42">
-        <v>43.14</v>
+        <v>44.631</v>
       </c>
       <c r="F42">
-        <v>59.64</v>
+        <v>61.131</v>
       </c>
       <c r="G42">
         <v>25.1</v>
@@ -4731,45 +4731,45 @@
         <v>15.16</v>
       </c>
       <c r="M42">
-        <v>3.298092</v>
+        <v>3.5333718</v>
       </c>
       <c r="N42">
-        <v>11.861908</v>
+        <v>11.6266282</v>
       </c>
       <c r="O42">
-        <v>2.13514344</v>
+        <v>2.092793076</v>
       </c>
       <c r="P42">
-        <v>9.726764559999999</v>
+        <v>9.533835123999999</v>
       </c>
       <c r="Q42">
-        <v>17.86676456</v>
+        <v>17.673835124</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1109960404673207</v>
+        <v>0.1119724569120753</v>
       </c>
       <c r="T42">
-        <v>1.099298904319577</v>
+        <v>1.115762688319103</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.18</v>
       </c>
       <c r="W42">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.596597062786605</v>
+        <v>4.290519327742413</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08549610957812444</v>
+        <v>0.08543619487585642</v>
       </c>
       <c r="C43">
-        <v>95.39623127168406</v>
+        <v>94.08385831138864</v>
       </c>
       <c r="D43">
-        <v>131.4272312716841</v>
+        <v>131.6058583113887</v>
       </c>
       <c r="E43">
-        <v>44.631</v>
+        <v>46.12200000000001</v>
       </c>
       <c r="F43">
-        <v>61.131</v>
+        <v>62.62200000000001</v>
       </c>
       <c r="G43">
         <v>25.1</v>
@@ -4813,28 +4813,28 @@
         <v>15.16</v>
       </c>
       <c r="M43">
-        <v>3.5333718</v>
+        <v>3.619551600000001</v>
       </c>
       <c r="N43">
-        <v>11.6266282</v>
+        <v>11.5404484</v>
       </c>
       <c r="O43">
-        <v>2.092793076</v>
+        <v>2.077280712</v>
       </c>
       <c r="P43">
-        <v>9.533835123999999</v>
+        <v>9.463167687999999</v>
       </c>
       <c r="Q43">
-        <v>17.673835124</v>
+        <v>17.603167688</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1119724569120753</v>
+        <v>0.1129825428894076</v>
       </c>
       <c r="T43">
-        <v>1.115762688319103</v>
+        <v>1.132794189008268</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.290519327742413</v>
+        <v>4.188364105653307</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08543619487585644</v>
+        <v>0.08537628017358842</v>
       </c>
       <c r="C44">
-        <v>94.08385831138861</v>
+        <v>92.77197156760579</v>
       </c>
       <c r="D44">
-        <v>131.6058583113886</v>
+        <v>131.7849715676058</v>
       </c>
       <c r="E44">
-        <v>46.12199999999999</v>
+        <v>47.613</v>
       </c>
       <c r="F44">
-        <v>62.62199999999999</v>
+        <v>64.113</v>
       </c>
       <c r="G44">
         <v>25.1</v>
@@ -4895,28 +4895,28 @@
         <v>15.16</v>
       </c>
       <c r="M44">
-        <v>3.6195516</v>
+        <v>3.7057314</v>
       </c>
       <c r="N44">
-        <v>11.5404484</v>
+        <v>11.4542686</v>
       </c>
       <c r="O44">
-        <v>2.077280712</v>
+        <v>2.061768348</v>
       </c>
       <c r="P44">
-        <v>9.463167688</v>
+        <v>9.392500252</v>
       </c>
       <c r="Q44">
-        <v>17.603167688</v>
+        <v>17.532500252</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1129825428894076</v>
+        <v>0.1140280704799797</v>
       </c>
       <c r="T44">
-        <v>1.132794189008268</v>
+        <v>1.150423286212842</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.188364105653308</v>
+        <v>4.090960289242766</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08537628017358842</v>
+        <v>0.08657916547132043</v>
       </c>
       <c r="C45">
-        <v>92.77197156760579</v>
+        <v>87.77586039469882</v>
       </c>
       <c r="D45">
-        <v>131.7849715676058</v>
+        <v>128.2798603946988</v>
       </c>
       <c r="E45">
-        <v>47.613</v>
+        <v>49.104</v>
       </c>
       <c r="F45">
-        <v>64.113</v>
+        <v>65.604</v>
       </c>
       <c r="G45">
         <v>25.1</v>
@@ -4977,45 +4977,45 @@
         <v>15.16</v>
       </c>
       <c r="M45">
-        <v>3.7057314</v>
+        <v>4.0215252</v>
       </c>
       <c r="N45">
-        <v>11.4542686</v>
+        <v>11.1384748</v>
       </c>
       <c r="O45">
-        <v>2.061768348</v>
+        <v>2.004925464</v>
       </c>
       <c r="P45">
-        <v>9.392500252</v>
+        <v>9.133549336000002</v>
       </c>
       <c r="Q45">
-        <v>17.532500252</v>
+        <v>17.273549336</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1140280704799797</v>
+        <v>0.1151109383416436</v>
       </c>
       <c r="T45">
-        <v>1.150423286212842</v>
+        <v>1.168681994031865</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.18</v>
       </c>
       <c r="W45">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.090960289242766</v>
+        <v>3.769714037848128</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08657916547132043</v>
+        <v>0.08654795076905242</v>
       </c>
       <c r="C46">
-        <v>87.77586039469882</v>
+        <v>86.37345947617399</v>
       </c>
       <c r="D46">
-        <v>128.2798603946988</v>
+        <v>128.368459476174</v>
       </c>
       <c r="E46">
-        <v>49.104</v>
+        <v>50.595</v>
       </c>
       <c r="F46">
-        <v>65.604</v>
+        <v>67.095</v>
       </c>
       <c r="G46">
         <v>25.1</v>
@@ -5059,28 +5059,28 @@
         <v>15.16</v>
       </c>
       <c r="M46">
-        <v>4.0215252</v>
+        <v>4.1129235</v>
       </c>
       <c r="N46">
-        <v>11.1384748</v>
+        <v>11.0470765</v>
       </c>
       <c r="O46">
-        <v>2.004925464</v>
+        <v>1.98847377</v>
       </c>
       <c r="P46">
-        <v>9.133549336000002</v>
+        <v>9.05860273</v>
       </c>
       <c r="Q46">
-        <v>17.273549336</v>
+        <v>17.19860273</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1151109383416436</v>
+        <v>0.1162331832164589</v>
       </c>
       <c r="T46">
-        <v>1.168681994031865</v>
+        <v>1.187604654862489</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.769714037848128</v>
+        <v>3.685942614784836</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08654795076905242</v>
+        <v>0.08651673606678442</v>
       </c>
       <c r="C47">
-        <v>86.37345947617399</v>
+        <v>84.97118102773267</v>
       </c>
       <c r="D47">
-        <v>128.368459476174</v>
+        <v>128.4571810277327</v>
       </c>
       <c r="E47">
-        <v>50.595</v>
+        <v>52.086</v>
       </c>
       <c r="F47">
-        <v>67.095</v>
+        <v>68.586</v>
       </c>
       <c r="G47">
         <v>25.1</v>
@@ -5141,28 +5141,28 @@
         <v>15.16</v>
       </c>
       <c r="M47">
-        <v>4.1129235</v>
+        <v>4.2043218</v>
       </c>
       <c r="N47">
-        <v>11.0470765</v>
+        <v>10.9556782</v>
       </c>
       <c r="O47">
-        <v>1.98847377</v>
+        <v>1.972022076</v>
       </c>
       <c r="P47">
-        <v>9.05860273</v>
+        <v>8.983656124000001</v>
       </c>
       <c r="Q47">
-        <v>17.19860273</v>
+        <v>17.123656124</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1162331832164589</v>
+        <v>0.1173969927162674</v>
       </c>
       <c r="T47">
-        <v>1.187604654862489</v>
+        <v>1.207228154983137</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.685942614784836</v>
+        <v>3.605813427506905</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08651673606678442</v>
+        <v>0.0864855213645164</v>
       </c>
       <c r="C48">
-        <v>84.97118102773267</v>
+        <v>83.56902530348523</v>
       </c>
       <c r="D48">
-        <v>128.4571810277327</v>
+        <v>128.5460253034852</v>
       </c>
       <c r="E48">
-        <v>52.086</v>
+        <v>53.577</v>
       </c>
       <c r="F48">
-        <v>68.586</v>
+        <v>70.077</v>
       </c>
       <c r="G48">
         <v>25.1</v>
@@ -5223,28 +5223,28 @@
         <v>15.16</v>
       </c>
       <c r="M48">
-        <v>4.2043218</v>
+        <v>4.2957201</v>
       </c>
       <c r="N48">
-        <v>10.9556782</v>
+        <v>10.8642799</v>
       </c>
       <c r="O48">
-        <v>1.972022076</v>
+        <v>1.955570382</v>
       </c>
       <c r="P48">
-        <v>8.983656124000001</v>
+        <v>8.908709518</v>
       </c>
       <c r="Q48">
-        <v>17.123656124</v>
+        <v>17.048709518</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1173969927162674</v>
+        <v>0.1186047195556913</v>
       </c>
       <c r="T48">
-        <v>1.207228154983137</v>
+        <v>1.227592164542299</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.605813427506905</v>
+        <v>3.529093992879099</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0864855213645164</v>
+        <v>0.08755638666224841</v>
       </c>
       <c r="C49">
-        <v>83.56902530348523</v>
+        <v>79.09867810032348</v>
       </c>
       <c r="D49">
-        <v>128.5460253034852</v>
+        <v>125.5666781003235</v>
       </c>
       <c r="E49">
-        <v>53.577</v>
+        <v>55.068</v>
       </c>
       <c r="F49">
-        <v>70.077</v>
+        <v>71.568</v>
       </c>
       <c r="G49">
         <v>25.1</v>
@@ -5305,45 +5305,45 @@
         <v>15.16</v>
       </c>
       <c r="M49">
-        <v>4.2957201</v>
+        <v>4.5875088</v>
       </c>
       <c r="N49">
-        <v>10.8642799</v>
+        <v>10.5724912</v>
       </c>
       <c r="O49">
-        <v>1.955570382</v>
+        <v>1.903048416</v>
       </c>
       <c r="P49">
-        <v>8.908709518</v>
+        <v>8.669442784000001</v>
       </c>
       <c r="Q49">
-        <v>17.048709518</v>
+        <v>16.809442784</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1186047195556913</v>
+        <v>0.1198588974274008</v>
       </c>
       <c r="T49">
-        <v>1.227592164542299</v>
+        <v>1.248739405238352</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.18</v>
       </c>
       <c r="W49">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.529093992879099</v>
+        <v>3.304625813469829</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08755638666224841</v>
+        <v>0.0875481319599804</v>
       </c>
       <c r="C50">
-        <v>79.09867810032348</v>
+        <v>77.63011593979707</v>
       </c>
       <c r="D50">
-        <v>125.5666781003235</v>
+        <v>125.5891159397971</v>
       </c>
       <c r="E50">
-        <v>55.068</v>
+        <v>56.559</v>
       </c>
       <c r="F50">
-        <v>71.568</v>
+        <v>73.059</v>
       </c>
       <c r="G50">
         <v>25.1</v>
@@ -5387,28 +5387,28 @@
         <v>15.16</v>
       </c>
       <c r="M50">
-        <v>4.5875088</v>
+        <v>4.6830819</v>
       </c>
       <c r="N50">
-        <v>10.5724912</v>
+        <v>10.4769181</v>
       </c>
       <c r="O50">
-        <v>1.903048416</v>
+        <v>1.885845258</v>
       </c>
       <c r="P50">
-        <v>8.669442784000001</v>
+        <v>8.591072841999999</v>
       </c>
       <c r="Q50">
-        <v>16.809442784</v>
+        <v>16.731072842</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1198588974274008</v>
+        <v>0.1211622587450596</v>
       </c>
       <c r="T50">
-        <v>1.248739405238352</v>
+        <v>1.270715949491113</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.304625813469829</v>
+        <v>3.237184470337791</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0875481319599804</v>
+        <v>0.0875398772577124</v>
       </c>
       <c r="C51">
-        <v>77.63011593979707</v>
+        <v>76.16156179965681</v>
       </c>
       <c r="D51">
-        <v>125.5891159397971</v>
+        <v>125.6115617996568</v>
       </c>
       <c r="E51">
-        <v>56.559</v>
+        <v>58.05</v>
       </c>
       <c r="F51">
-        <v>73.059</v>
+        <v>74.55</v>
       </c>
       <c r="G51">
         <v>25.1</v>
@@ -5469,28 +5469,28 @@
         <v>15.16</v>
       </c>
       <c r="M51">
-        <v>4.6830819</v>
+        <v>4.778655000000001</v>
       </c>
       <c r="N51">
-        <v>10.4769181</v>
+        <v>10.381345</v>
       </c>
       <c r="O51">
-        <v>1.885845258</v>
+        <v>1.8686421</v>
       </c>
       <c r="P51">
-        <v>8.591072841999999</v>
+        <v>8.512702900000001</v>
       </c>
       <c r="Q51">
-        <v>16.731072842</v>
+        <v>16.6527029</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1211622587450596</v>
+        <v>0.1225177545154248</v>
       </c>
       <c r="T51">
-        <v>1.270715949491113</v>
+        <v>1.293571555513985</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.237184470337791</v>
+        <v>3.172440780931036</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0875398772577124</v>
+        <v>0.0875316225554444</v>
       </c>
       <c r="C52">
-        <v>76.16156179965681</v>
+        <v>74.69301568420369</v>
       </c>
       <c r="D52">
-        <v>125.6115617996568</v>
+        <v>125.6340156842037</v>
       </c>
       <c r="E52">
-        <v>58.05</v>
+        <v>59.541</v>
       </c>
       <c r="F52">
-        <v>74.55</v>
+        <v>76.041</v>
       </c>
       <c r="G52">
         <v>25.1</v>
@@ -5551,28 +5551,28 @@
         <v>15.16</v>
       </c>
       <c r="M52">
-        <v>4.778655000000001</v>
+        <v>4.8742281</v>
       </c>
       <c r="N52">
-        <v>10.381345</v>
+        <v>10.2857719</v>
       </c>
       <c r="O52">
-        <v>1.8686421</v>
+        <v>1.851438942</v>
       </c>
       <c r="P52">
-        <v>8.512702900000001</v>
+        <v>8.434332958000001</v>
       </c>
       <c r="Q52">
-        <v>16.6527029</v>
+        <v>16.574332958</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1225177545154248</v>
+        <v>0.1239285766437641</v>
       </c>
       <c r="T52">
-        <v>1.293571555513985</v>
+        <v>1.317360043415341</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.172440780931036</v>
+        <v>3.11023605973631</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0875316225554444</v>
+        <v>0.0875233678531764</v>
       </c>
       <c r="C53">
-        <v>74.69301568420369</v>
+        <v>73.22447759774194</v>
       </c>
       <c r="D53">
-        <v>125.6340156842037</v>
+        <v>125.6564775977419</v>
       </c>
       <c r="E53">
-        <v>59.541</v>
+        <v>61.032</v>
       </c>
       <c r="F53">
-        <v>76.041</v>
+        <v>77.532</v>
       </c>
       <c r="G53">
         <v>25.1</v>
@@ -5633,28 +5633,28 @@
         <v>15.16</v>
       </c>
       <c r="M53">
-        <v>4.8742281</v>
+        <v>4.9698012</v>
       </c>
       <c r="N53">
-        <v>10.2857719</v>
+        <v>10.1901988</v>
       </c>
       <c r="O53">
-        <v>1.851438942</v>
+        <v>1.834235784</v>
       </c>
       <c r="P53">
-        <v>8.434332958000001</v>
+        <v>8.355963016</v>
       </c>
       <c r="Q53">
-        <v>16.574332958</v>
+        <v>16.495963016</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1239285766437641</v>
+        <v>0.1253981830274508</v>
       </c>
       <c r="T53">
-        <v>1.317360043415341</v>
+        <v>1.342139718312587</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.11023605973631</v>
+        <v>3.050423827818304</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0875233678531764</v>
+        <v>0.09090499315090839</v>
       </c>
       <c r="C54">
-        <v>73.22447759774194</v>
+        <v>63.15815295815815</v>
       </c>
       <c r="D54">
-        <v>125.6564775977419</v>
+        <v>117.0811529581582</v>
       </c>
       <c r="E54">
-        <v>61.032</v>
+        <v>62.523</v>
       </c>
       <c r="F54">
-        <v>77.532</v>
+        <v>79.023</v>
       </c>
       <c r="G54">
         <v>25.1</v>
@@ -5715,45 +5715,45 @@
         <v>15.16</v>
       </c>
       <c r="M54">
-        <v>4.9698012</v>
+        <v>5.6817537</v>
       </c>
       <c r="N54">
-        <v>10.1901988</v>
+        <v>9.4782463</v>
       </c>
       <c r="O54">
-        <v>1.834235784</v>
+        <v>1.706084334</v>
       </c>
       <c r="P54">
-        <v>8.355963016</v>
+        <v>7.772161966000001</v>
       </c>
       <c r="Q54">
-        <v>16.495963016</v>
+        <v>15.912161966</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1253981830274508</v>
+        <v>0.1269303258529966</v>
       </c>
       <c r="T54">
-        <v>1.342139718312587</v>
+        <v>1.367973847460779</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.18</v>
       </c>
       <c r="W54">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.050423827818304</v>
+        <v>2.668190280757858</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09090499315090839</v>
+        <v>0.09096069844864038</v>
       </c>
       <c r="C55">
-        <v>63.15815295815815</v>
+        <v>61.53568020925427</v>
       </c>
       <c r="D55">
-        <v>117.0811529581582</v>
+        <v>116.9496802092543</v>
       </c>
       <c r="E55">
-        <v>62.523</v>
+        <v>64.014</v>
       </c>
       <c r="F55">
-        <v>79.023</v>
+        <v>80.514</v>
       </c>
       <c r="G55">
         <v>25.1</v>
@@ -5797,28 +5797,28 @@
         <v>15.16</v>
       </c>
       <c r="M55">
-        <v>5.6817537</v>
+        <v>5.788956600000001</v>
       </c>
       <c r="N55">
-        <v>9.4782463</v>
+        <v>9.3710434</v>
       </c>
       <c r="O55">
-        <v>1.706084334</v>
+        <v>1.686787812</v>
       </c>
       <c r="P55">
-        <v>7.772161966000001</v>
+        <v>7.684255587999999</v>
       </c>
       <c r="Q55">
-        <v>15.912161966</v>
+        <v>15.824255588</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1269303258529966</v>
+        <v>0.1285290835840008</v>
       </c>
       <c r="T55">
-        <v>1.367973847460779</v>
+        <v>1.394931199615415</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.668190280757858</v>
+        <v>2.618779349632713</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09096069844864038</v>
+        <v>0.09101640374637239</v>
       </c>
       <c r="C56">
-        <v>61.53568020925427</v>
+        <v>59.91350239587628</v>
       </c>
       <c r="D56">
-        <v>116.9496802092543</v>
+        <v>116.8185023958763</v>
       </c>
       <c r="E56">
-        <v>64.014</v>
+        <v>65.50500000000001</v>
       </c>
       <c r="F56">
-        <v>80.514</v>
+        <v>82.00500000000001</v>
       </c>
       <c r="G56">
         <v>25.1</v>
@@ -5879,28 +5879,28 @@
         <v>15.16</v>
       </c>
       <c r="M56">
-        <v>5.788956600000001</v>
+        <v>5.896159500000001</v>
       </c>
       <c r="N56">
-        <v>9.3710434</v>
+        <v>9.263840499999999</v>
       </c>
       <c r="O56">
-        <v>1.686787812</v>
+        <v>1.66749129</v>
       </c>
       <c r="P56">
-        <v>7.684255587999999</v>
+        <v>7.59634921</v>
       </c>
       <c r="Q56">
-        <v>15.824255588</v>
+        <v>15.73634921</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1285290835840008</v>
+        <v>0.1301988972141609</v>
       </c>
       <c r="T56">
-        <v>1.394931199615415</v>
+        <v>1.423086656310257</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.618779349632713</v>
+        <v>2.57116517963939</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09101640374637239</v>
+        <v>0.09107210904410439</v>
       </c>
       <c r="C57">
-        <v>59.91350239587628</v>
+        <v>58.29161852668378</v>
       </c>
       <c r="D57">
-        <v>116.8185023958763</v>
+        <v>116.6876185266838</v>
       </c>
       <c r="E57">
-        <v>65.50500000000001</v>
+        <v>66.99600000000001</v>
       </c>
       <c r="F57">
-        <v>82.00500000000001</v>
+        <v>83.49600000000001</v>
       </c>
       <c r="G57">
         <v>25.1</v>
@@ -5961,28 +5961,28 @@
         <v>15.16</v>
       </c>
       <c r="M57">
-        <v>5.896159500000001</v>
+        <v>6.003362400000001</v>
       </c>
       <c r="N57">
-        <v>9.263840499999999</v>
+        <v>9.1566376</v>
       </c>
       <c r="O57">
-        <v>1.66749129</v>
+        <v>1.648194768</v>
       </c>
       <c r="P57">
-        <v>7.59634921</v>
+        <v>7.508442832</v>
       </c>
       <c r="Q57">
-        <v>15.73634921</v>
+        <v>15.648442832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1301988972141609</v>
+        <v>0.1319446114638736</v>
       </c>
       <c r="T57">
-        <v>1.423086656310257</v>
+        <v>1.452521906491228</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.57116517963939</v>
+        <v>2.525251515717258</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09107210904410439</v>
+        <v>0.09295067434183639</v>
       </c>
       <c r="C58">
-        <v>58.29161852668378</v>
+        <v>52.55224958703296</v>
       </c>
       <c r="D58">
-        <v>116.6876185266838</v>
+        <v>112.439249587033</v>
       </c>
       <c r="E58">
-        <v>66.99600000000001</v>
+        <v>68.48700000000001</v>
       </c>
       <c r="F58">
-        <v>83.49600000000001</v>
+        <v>84.98700000000001</v>
       </c>
       <c r="G58">
         <v>25.1</v>
@@ -6043,45 +6043,45 @@
         <v>15.16</v>
       </c>
       <c r="M58">
-        <v>6.003362400000001</v>
+        <v>6.442014600000001</v>
       </c>
       <c r="N58">
-        <v>9.1566376</v>
+        <v>8.7179854</v>
       </c>
       <c r="O58">
-        <v>1.648194768</v>
+        <v>1.569237372</v>
       </c>
       <c r="P58">
-        <v>7.508442832</v>
+        <v>7.148748028</v>
       </c>
       <c r="Q58">
-        <v>15.648442832</v>
+        <v>15.288748028</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1319446114638736</v>
+        <v>0.1337715217252009</v>
       </c>
       <c r="T58">
-        <v>1.452521906491228</v>
+        <v>1.483326238075965</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.18</v>
       </c>
       <c r="W58">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.525251515717258</v>
+        <v>2.353301093108358</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09295067434183639</v>
+        <v>0.09303835963956839</v>
       </c>
       <c r="C59">
-        <v>52.55224958703296</v>
+        <v>50.8704934781411</v>
       </c>
       <c r="D59">
-        <v>112.439249587033</v>
+        <v>112.2484934781411</v>
       </c>
       <c r="E59">
-        <v>68.48700000000001</v>
+        <v>69.97800000000001</v>
       </c>
       <c r="F59">
-        <v>84.98700000000001</v>
+        <v>86.47800000000001</v>
       </c>
       <c r="G59">
         <v>25.1</v>
@@ -6125,28 +6125,28 @@
         <v>15.16</v>
       </c>
       <c r="M59">
-        <v>6.442014600000001</v>
+        <v>6.555032400000001</v>
       </c>
       <c r="N59">
-        <v>8.7179854</v>
+        <v>8.604967599999998</v>
       </c>
       <c r="O59">
-        <v>1.569237372</v>
+        <v>1.548894168</v>
       </c>
       <c r="P59">
-        <v>7.148748028</v>
+        <v>7.056073431999999</v>
       </c>
       <c r="Q59">
-        <v>15.288748028</v>
+        <v>15.196073432</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1337715217252009</v>
+        <v>0.1356854277132581</v>
       </c>
       <c r="T59">
-        <v>1.483326238075965</v>
+        <v>1.515597442593308</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.353301093108358</v>
+        <v>2.312726936330627</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09303835963956839</v>
+        <v>0.09312604493730037</v>
       </c>
       <c r="C60">
-        <v>50.87049347814111</v>
+        <v>49.18938351843227</v>
       </c>
       <c r="D60">
-        <v>112.2484934781411</v>
+        <v>112.0583835184323</v>
       </c>
       <c r="E60">
-        <v>69.97799999999999</v>
+        <v>71.46899999999999</v>
       </c>
       <c r="F60">
-        <v>86.47799999999999</v>
+        <v>87.96899999999999</v>
       </c>
       <c r="G60">
         <v>25.1</v>
@@ -6207,28 +6207,28 @@
         <v>15.16</v>
       </c>
       <c r="M60">
-        <v>6.5550324</v>
+        <v>6.6680502</v>
       </c>
       <c r="N60">
-        <v>8.6049676</v>
+        <v>8.4919498</v>
       </c>
       <c r="O60">
-        <v>1.548894168</v>
+        <v>1.528550964</v>
       </c>
       <c r="P60">
-        <v>7.056073432</v>
+        <v>6.963398836000001</v>
       </c>
       <c r="Q60">
-        <v>15.196073432</v>
+        <v>15.103398836</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.135685427713258</v>
+        <v>0.1376926949690253</v>
       </c>
       <c r="T60">
-        <v>1.515597442593308</v>
+        <v>1.549442852209058</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.312726936330628</v>
+        <v>2.273528174697905</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09312604493730037</v>
+        <v>0.09321373023503238</v>
       </c>
       <c r="C61">
-        <v>49.18938351843227</v>
+        <v>47.50891643040042</v>
       </c>
       <c r="D61">
-        <v>112.0583835184323</v>
+        <v>111.8689164304004</v>
       </c>
       <c r="E61">
-        <v>71.46899999999999</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="F61">
-        <v>87.96899999999999</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G61">
         <v>25.1</v>
@@ -6289,28 +6289,28 @@
         <v>15.16</v>
       </c>
       <c r="M61">
-        <v>6.6680502</v>
+        <v>6.781068</v>
       </c>
       <c r="N61">
-        <v>8.4919498</v>
+        <v>8.378931999999999</v>
       </c>
       <c r="O61">
-        <v>1.528550964</v>
+        <v>1.50820776</v>
       </c>
       <c r="P61">
-        <v>6.963398836000001</v>
+        <v>6.870724239999999</v>
       </c>
       <c r="Q61">
-        <v>15.103398836</v>
+        <v>15.01072424</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1376926949690253</v>
+        <v>0.1398003255875809</v>
       </c>
       <c r="T61">
-        <v>1.549442852209058</v>
+        <v>1.584980532305597</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.273528174697905</v>
+        <v>2.23563603845294</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09321373023503238</v>
+        <v>0.09330141553276439</v>
       </c>
       <c r="C62">
-        <v>47.50891643040042</v>
+        <v>45.82908895866862</v>
       </c>
       <c r="D62">
-        <v>111.8689164304004</v>
+        <v>111.6800889586686</v>
       </c>
       <c r="E62">
-        <v>72.95999999999999</v>
+        <v>74.45099999999999</v>
       </c>
       <c r="F62">
-        <v>89.45999999999999</v>
+        <v>90.95099999999999</v>
       </c>
       <c r="G62">
         <v>25.1</v>
@@ -6371,28 +6371,28 @@
         <v>15.16</v>
       </c>
       <c r="M62">
-        <v>6.781068</v>
+        <v>6.8940858</v>
       </c>
       <c r="N62">
-        <v>8.378931999999999</v>
+        <v>8.265914200000001</v>
       </c>
       <c r="O62">
-        <v>1.50820776</v>
+        <v>1.487864556</v>
       </c>
       <c r="P62">
-        <v>6.870724239999999</v>
+        <v>6.778049644000001</v>
       </c>
       <c r="Q62">
-        <v>15.01072424</v>
+        <v>14.918049644</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1398003255875809</v>
+        <v>0.142016039827601</v>
       </c>
       <c r="T62">
-        <v>1.584980532305597</v>
+        <v>1.622340657535291</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.23563603845294</v>
+        <v>2.198986267330761</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09330141553276439</v>
+        <v>0.09338910083049637</v>
       </c>
       <c r="C63">
-        <v>45.82908895866862</v>
+        <v>44.14989786980236</v>
       </c>
       <c r="D63">
-        <v>111.6800889586686</v>
+        <v>111.4918978698024</v>
       </c>
       <c r="E63">
-        <v>74.45099999999999</v>
+        <v>75.94199999999999</v>
       </c>
       <c r="F63">
-        <v>90.95099999999999</v>
+        <v>92.44199999999999</v>
       </c>
       <c r="G63">
         <v>25.1</v>
@@ -6453,28 +6453,28 @@
         <v>15.16</v>
       </c>
       <c r="M63">
-        <v>6.8940858</v>
+        <v>7.0071036</v>
       </c>
       <c r="N63">
-        <v>8.265914200000001</v>
+        <v>8.152896399999999</v>
       </c>
       <c r="O63">
-        <v>1.487864556</v>
+        <v>1.467521352</v>
       </c>
       <c r="P63">
-        <v>6.778049644000001</v>
+        <v>6.685375047999999</v>
       </c>
       <c r="Q63">
-        <v>14.918049644</v>
+        <v>14.825375048</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.142016039827601</v>
+        <v>0.1443483706065694</v>
       </c>
       <c r="T63">
-        <v>1.622340657535291</v>
+        <v>1.661667105145494</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.198986267330761</v>
+        <v>2.163518746889942</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09338910083049637</v>
+        <v>0.09347678612822836</v>
       </c>
       <c r="C64">
-        <v>44.14989786980236</v>
+        <v>42.47133995212479</v>
       </c>
       <c r="D64">
-        <v>111.4918978698024</v>
+        <v>111.3043399521248</v>
       </c>
       <c r="E64">
-        <v>75.94199999999999</v>
+        <v>77.43299999999999</v>
       </c>
       <c r="F64">
-        <v>92.44199999999999</v>
+        <v>93.93299999999999</v>
       </c>
       <c r="G64">
         <v>25.1</v>
@@ -6535,28 +6535,28 @@
         <v>15.16</v>
       </c>
       <c r="M64">
-        <v>7.0071036</v>
+        <v>7.1201214</v>
       </c>
       <c r="N64">
-        <v>8.152896399999999</v>
+        <v>8.0398786</v>
       </c>
       <c r="O64">
-        <v>1.467521352</v>
+        <v>1.447178148</v>
       </c>
       <c r="P64">
-        <v>6.685375047999999</v>
+        <v>6.592700452</v>
       </c>
       <c r="Q64">
-        <v>14.825375048</v>
+        <v>14.732700452</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1443483706065694</v>
+        <v>0.1468067733195361</v>
       </c>
       <c r="T64">
-        <v>1.661667105145494</v>
+        <v>1.703119306680574</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.163518746889942</v>
+        <v>2.12917717947899</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09347678612822836</v>
+        <v>0.09356447142596037</v>
       </c>
       <c r="C65">
-        <v>42.47133995212479</v>
+        <v>40.79341201553432</v>
       </c>
       <c r="D65">
-        <v>111.3043399521248</v>
+        <v>111.1174120155343</v>
       </c>
       <c r="E65">
-        <v>77.43299999999999</v>
+        <v>78.92399999999999</v>
       </c>
       <c r="F65">
-        <v>93.93299999999999</v>
+        <v>95.42399999999999</v>
       </c>
       <c r="G65">
         <v>25.1</v>
@@ -6617,28 +6617,28 @@
         <v>15.16</v>
       </c>
       <c r="M65">
-        <v>7.1201214</v>
+        <v>7.2331392</v>
       </c>
       <c r="N65">
-        <v>8.0398786</v>
+        <v>7.9268608</v>
       </c>
       <c r="O65">
-        <v>1.447178148</v>
+        <v>1.426834944</v>
       </c>
       <c r="P65">
-        <v>6.592700452</v>
+        <v>6.500025856000001</v>
       </c>
       <c r="Q65">
-        <v>14.732700452</v>
+        <v>14.640025856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1468067733195361</v>
+        <v>0.149401753961001</v>
       </c>
       <c r="T65">
-        <v>1.703119306680574</v>
+        <v>1.746874408300937</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.12917717947899</v>
+        <v>2.095908786049631</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09356447142596037</v>
+        <v>0.09365215672369237</v>
       </c>
       <c r="C66">
-        <v>40.79341201553432</v>
+        <v>39.11611089132369</v>
       </c>
       <c r="D66">
-        <v>111.1174120155343</v>
+        <v>110.9311108913237</v>
       </c>
       <c r="E66">
-        <v>78.92399999999999</v>
+        <v>80.41500000000001</v>
       </c>
       <c r="F66">
-        <v>95.42399999999999</v>
+        <v>96.91500000000001</v>
       </c>
       <c r="G66">
         <v>25.1</v>
@@ -6699,28 +6699,28 @@
         <v>15.16</v>
       </c>
       <c r="M66">
-        <v>7.2331392</v>
+        <v>7.346157000000001</v>
       </c>
       <c r="N66">
-        <v>7.9268608</v>
+        <v>7.813842999999999</v>
       </c>
       <c r="O66">
-        <v>1.426834944</v>
+        <v>1.40649174</v>
       </c>
       <c r="P66">
-        <v>6.500025856000001</v>
+        <v>6.40735126</v>
       </c>
       <c r="Q66">
-        <v>14.640025856</v>
+        <v>14.54735126</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.149401753961001</v>
+        <v>0.1521450192105496</v>
       </c>
       <c r="T66">
-        <v>1.746874408300937</v>
+        <v>1.793129801442462</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.095908786049631</v>
+        <v>2.063664035495021</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09365215672369237</v>
+        <v>0.09373984202142437</v>
       </c>
       <c r="C67">
-        <v>39.11611089132369</v>
+        <v>37.43943343200084</v>
       </c>
       <c r="D67">
-        <v>110.9311108913237</v>
+        <v>110.7454334320009</v>
       </c>
       <c r="E67">
-        <v>80.41500000000001</v>
+        <v>81.90600000000001</v>
       </c>
       <c r="F67">
-        <v>96.91500000000001</v>
+        <v>98.40600000000001</v>
       </c>
       <c r="G67">
         <v>25.1</v>
@@ -6781,28 +6781,28 @@
         <v>15.16</v>
       </c>
       <c r="M67">
-        <v>7.346157000000001</v>
+        <v>7.459174800000001</v>
       </c>
       <c r="N67">
-        <v>7.813842999999999</v>
+        <v>7.700825199999999</v>
       </c>
       <c r="O67">
-        <v>1.40649174</v>
+        <v>1.386148536</v>
       </c>
       <c r="P67">
-        <v>6.40735126</v>
+        <v>6.314676663999999</v>
       </c>
       <c r="Q67">
-        <v>14.54735126</v>
+        <v>14.454676664</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1521450192105496</v>
+        <v>0.1550496530041893</v>
       </c>
       <c r="T67">
-        <v>1.793129801442462</v>
+        <v>1.842106100062901</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.063664035495021</v>
+        <v>2.032396398593582</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09373984202142437</v>
+        <v>0.09382752731915636</v>
       </c>
       <c r="C68">
-        <v>37.43943343200084</v>
+        <v>35.7633765111117</v>
       </c>
       <c r="D68">
-        <v>110.7454334320009</v>
+        <v>110.5603765111117</v>
       </c>
       <c r="E68">
-        <v>81.90600000000001</v>
+        <v>83.39700000000001</v>
       </c>
       <c r="F68">
-        <v>98.40600000000001</v>
+        <v>99.89700000000001</v>
       </c>
       <c r="G68">
         <v>25.1</v>
@@ -6863,28 +6863,28 @@
         <v>15.16</v>
       </c>
       <c r="M68">
-        <v>7.459174800000001</v>
+        <v>7.572192600000001</v>
       </c>
       <c r="N68">
-        <v>7.700825199999999</v>
+        <v>7.587807399999999</v>
       </c>
       <c r="O68">
-        <v>1.386148536</v>
+        <v>1.365805332</v>
       </c>
       <c r="P68">
-        <v>6.314676663999999</v>
+        <v>6.222002067999999</v>
       </c>
       <c r="Q68">
-        <v>14.454676664</v>
+        <v>14.362002068</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1550496530041893</v>
+        <v>0.1581303252095647</v>
       </c>
       <c r="T68">
-        <v>1.842106100062901</v>
+        <v>1.894050659205791</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.032396398593582</v>
+        <v>2.002062123987707</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09382752731915636</v>
+        <v>0.1018331326168884</v>
       </c>
       <c r="C69">
-        <v>35.7633765111117</v>
+        <v>19.63773661197419</v>
       </c>
       <c r="D69">
-        <v>110.5603765111117</v>
+        <v>95.9257366119742</v>
       </c>
       <c r="E69">
-        <v>83.39700000000001</v>
+        <v>84.88800000000001</v>
       </c>
       <c r="F69">
-        <v>99.89700000000001</v>
+        <v>101.388</v>
       </c>
       <c r="G69">
         <v>25.1</v>
@@ -6945,45 +6945,45 @@
         <v>15.16</v>
       </c>
       <c r="M69">
-        <v>7.572192600000001</v>
+        <v>9.124919999999999</v>
       </c>
       <c r="N69">
-        <v>7.587807399999999</v>
+        <v>6.035080000000001</v>
       </c>
       <c r="O69">
-        <v>1.365805332</v>
+        <v>1.0863144</v>
       </c>
       <c r="P69">
-        <v>6.222002067999999</v>
+        <v>4.948765600000001</v>
       </c>
       <c r="Q69">
-        <v>14.362002068</v>
+        <v>13.0887656</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1581303252095647</v>
+        <v>0.1614035394277761</v>
       </c>
       <c r="T69">
-        <v>1.894050659205791</v>
+        <v>1.949241753295112</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.18</v>
       </c>
       <c r="W69">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.002062123987707</v>
+        <v>1.661384428575812</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1018331326168884</v>
+        <v>0.1020372579146204</v>
       </c>
       <c r="C70">
-        <v>19.63773661197419</v>
+        <v>17.82406777992271</v>
       </c>
       <c r="D70">
-        <v>95.9257366119742</v>
+        <v>95.60306777992271</v>
       </c>
       <c r="E70">
-        <v>84.88800000000001</v>
+        <v>86.379</v>
       </c>
       <c r="F70">
-        <v>101.388</v>
+        <v>102.879</v>
       </c>
       <c r="G70">
         <v>25.1</v>
@@ -7027,28 +7027,28 @@
         <v>15.16</v>
       </c>
       <c r="M70">
-        <v>9.124919999999999</v>
+        <v>9.25911</v>
       </c>
       <c r="N70">
-        <v>6.035080000000001</v>
+        <v>5.90089</v>
       </c>
       <c r="O70">
-        <v>1.0863144</v>
+        <v>1.0621602</v>
       </c>
       <c r="P70">
-        <v>4.948765600000001</v>
+        <v>4.8387298</v>
       </c>
       <c r="Q70">
-        <v>13.0887656</v>
+        <v>12.9787298</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1614035394277761</v>
+        <v>0.1648879287568399</v>
       </c>
       <c r="T70">
-        <v>1.949241753295112</v>
+        <v>2.007993563132131</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.661384428575812</v>
+        <v>1.637306393379061</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1020372579146204</v>
+        <v>0.1022413832123523</v>
       </c>
       <c r="C71">
-        <v>17.82406777992271</v>
+        <v>16.01256241592455</v>
       </c>
       <c r="D71">
-        <v>95.60306777992271</v>
+        <v>95.28256241592455</v>
       </c>
       <c r="E71">
-        <v>86.379</v>
+        <v>87.87</v>
       </c>
       <c r="F71">
-        <v>102.879</v>
+        <v>104.37</v>
       </c>
       <c r="G71">
         <v>25.1</v>
@@ -7109,28 +7109,28 @@
         <v>15.16</v>
       </c>
       <c r="M71">
-        <v>9.25911</v>
+        <v>9.3933</v>
       </c>
       <c r="N71">
-        <v>5.90089</v>
+        <v>5.7667</v>
       </c>
       <c r="O71">
-        <v>1.0621602</v>
+        <v>1.038006</v>
       </c>
       <c r="P71">
-        <v>4.8387298</v>
+        <v>4.728694</v>
       </c>
       <c r="Q71">
-        <v>12.9787298</v>
+        <v>12.868694</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1648879287568399</v>
+        <v>0.1686046107078412</v>
       </c>
       <c r="T71">
-        <v>2.007993563132131</v>
+        <v>2.070662160291617</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.637306393379061</v>
+        <v>1.613916302045075</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1022413832123523</v>
+        <v>0.1024455085100844</v>
       </c>
       <c r="C72">
-        <v>16.01256241592455</v>
+        <v>14.2031988338676</v>
       </c>
       <c r="D72">
-        <v>95.28256241592455</v>
+        <v>94.9641988338676</v>
       </c>
       <c r="E72">
-        <v>87.87</v>
+        <v>89.361</v>
       </c>
       <c r="F72">
-        <v>104.37</v>
+        <v>105.861</v>
       </c>
       <c r="G72">
         <v>25.1</v>
@@ -7191,28 +7191,28 @@
         <v>15.16</v>
       </c>
       <c r="M72">
-        <v>9.3933</v>
+        <v>9.52749</v>
       </c>
       <c r="N72">
-        <v>5.7667</v>
+        <v>5.63251</v>
       </c>
       <c r="O72">
-        <v>1.038006</v>
+        <v>1.0138518</v>
       </c>
       <c r="P72">
-        <v>4.728694</v>
+        <v>4.6186582</v>
       </c>
       <c r="Q72">
-        <v>12.868694</v>
+        <v>12.7586582</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1686046107078412</v>
+        <v>0.172577615552015</v>
       </c>
       <c r="T72">
-        <v>2.070662160291617</v>
+        <v>2.137652729668999</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.613916302045075</v>
+        <v>1.591185086523313</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1024455085100844</v>
+        <v>0.1026496338078163</v>
       </c>
       <c r="C73">
-        <v>14.20319883386762</v>
+        <v>12.39595563651035</v>
       </c>
       <c r="D73">
-        <v>94.9641988338676</v>
+        <v>94.64795563651035</v>
       </c>
       <c r="E73">
-        <v>89.36099999999999</v>
+        <v>90.85199999999999</v>
       </c>
       <c r="F73">
-        <v>105.861</v>
+        <v>107.352</v>
       </c>
       <c r="G73">
         <v>25.1</v>
@@ -7273,28 +7273,28 @@
         <v>15.16</v>
       </c>
       <c r="M73">
-        <v>9.527489999999998</v>
+        <v>9.661679999999999</v>
       </c>
       <c r="N73">
-        <v>5.632510000000002</v>
+        <v>5.498320000000001</v>
       </c>
       <c r="O73">
-        <v>1.0138518</v>
+        <v>0.9896976000000002</v>
       </c>
       <c r="P73">
-        <v>4.618658200000001</v>
+        <v>4.508622400000001</v>
       </c>
       <c r="Q73">
-        <v>12.7586582</v>
+        <v>12.6486224</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.172577615552015</v>
+        <v>0.1768344064564869</v>
       </c>
       <c r="T73">
-        <v>2.137652729668998</v>
+        <v>2.209428339716193</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.591185086523313</v>
+        <v>1.569085293654934</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1026496338078163</v>
+        <v>0.1028537591055483</v>
       </c>
       <c r="C74">
-        <v>12.39595563651035</v>
+        <v>10.5908117106876</v>
       </c>
       <c r="D74">
-        <v>94.64795563651035</v>
+        <v>94.3338117106876</v>
       </c>
       <c r="E74">
-        <v>90.85199999999999</v>
+        <v>92.34299999999999</v>
       </c>
       <c r="F74">
-        <v>107.352</v>
+        <v>108.843</v>
       </c>
       <c r="G74">
         <v>25.1</v>
@@ -7355,28 +7355,28 @@
         <v>15.16</v>
       </c>
       <c r="M74">
-        <v>9.661679999999999</v>
+        <v>9.795869999999999</v>
       </c>
       <c r="N74">
-        <v>5.498320000000001</v>
+        <v>5.364130000000001</v>
       </c>
       <c r="O74">
-        <v>0.9896976000000002</v>
+        <v>0.9655434000000002</v>
       </c>
       <c r="P74">
-        <v>4.508622400000001</v>
+        <v>4.398586600000001</v>
       </c>
       <c r="Q74">
-        <v>12.6486224</v>
+        <v>12.5385866</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1768344064564869</v>
+        <v>0.1814065152057346</v>
       </c>
       <c r="T74">
-        <v>2.209428339716193</v>
+        <v>2.286520661618736</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.569085293654934</v>
+        <v>1.54759097456377</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1028537591055483</v>
+        <v>0.1030578844032803</v>
       </c>
       <c r="C75">
-        <v>10.5908117106876</v>
+        <v>8.787746222611801</v>
       </c>
       <c r="D75">
-        <v>94.3338117106876</v>
+        <v>94.02174622261178</v>
       </c>
       <c r="E75">
-        <v>92.34299999999999</v>
+        <v>93.83399999999999</v>
       </c>
       <c r="F75">
-        <v>108.843</v>
+        <v>110.334</v>
       </c>
       <c r="G75">
         <v>25.1</v>
@@ -7437,28 +7437,28 @@
         <v>15.16</v>
       </c>
       <c r="M75">
-        <v>9.795869999999999</v>
+        <v>9.930059999999999</v>
       </c>
       <c r="N75">
-        <v>5.364130000000001</v>
+        <v>5.229940000000001</v>
       </c>
       <c r="O75">
-        <v>0.9655434000000002</v>
+        <v>0.9413892000000001</v>
       </c>
       <c r="P75">
-        <v>4.398586600000001</v>
+        <v>4.288550800000001</v>
       </c>
       <c r="Q75">
-        <v>12.5385866</v>
+        <v>12.4285508</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1814065152057346</v>
+        <v>0.1863303246280013</v>
       </c>
       <c r="T75">
-        <v>2.286520661618736</v>
+        <v>2.369543162129167</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.54759097456377</v>
+        <v>1.526677583015611</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1030578844032803</v>
+        <v>0.1032620097010123</v>
       </c>
       <c r="C76">
-        <v>8.787746222611801</v>
+        <v>6.986738613267335</v>
       </c>
       <c r="D76">
-        <v>94.02174622261178</v>
+        <v>93.71173861326733</v>
       </c>
       <c r="E76">
-        <v>93.83399999999999</v>
+        <v>95.32499999999999</v>
       </c>
       <c r="F76">
-        <v>110.334</v>
+        <v>111.825</v>
       </c>
       <c r="G76">
         <v>25.1</v>
@@ -7519,28 +7519,28 @@
         <v>15.16</v>
       </c>
       <c r="M76">
-        <v>9.930059999999999</v>
+        <v>10.06425</v>
       </c>
       <c r="N76">
-        <v>5.229940000000001</v>
+        <v>5.095750000000001</v>
       </c>
       <c r="O76">
-        <v>0.9413892000000001</v>
+        <v>0.9172350000000001</v>
       </c>
       <c r="P76">
-        <v>4.288550800000001</v>
+        <v>4.178515000000001</v>
       </c>
       <c r="Q76">
-        <v>12.4285508</v>
+        <v>12.318515</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1863303246280013</v>
+        <v>0.1916480388040493</v>
       </c>
       <c r="T76">
-        <v>2.369543162129167</v>
+        <v>2.459207462680432</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.526677583015611</v>
+        <v>1.506321881908737</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1032620097010123</v>
+        <v>0.1411555621388245</v>
       </c>
       <c r="C77">
-        <v>6.986738613267335</v>
+        <v>-30.08527270632393</v>
       </c>
       <c r="D77">
-        <v>93.71173861326733</v>
+        <v>58.13072729367607</v>
       </c>
       <c r="E77">
-        <v>95.32499999999999</v>
+        <v>96.816</v>
       </c>
       <c r="F77">
-        <v>111.825</v>
+        <v>113.316</v>
       </c>
       <c r="G77">
         <v>25.1</v>
@@ -7601,45 +7601,45 @@
         <v>15.16</v>
       </c>
       <c r="M77">
-        <v>10.06425</v>
+        <v>16.6347888</v>
       </c>
       <c r="N77">
-        <v>5.095750000000001</v>
+        <v>-1.474788800000002</v>
       </c>
       <c r="O77">
-        <v>0.9172350000000001</v>
+        <v>-0.2654619840000004</v>
       </c>
       <c r="P77">
-        <v>4.178515000000001</v>
+        <v>-1.209326816000002</v>
       </c>
       <c r="Q77">
-        <v>12.318515</v>
+        <v>6.930673183999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1916480388040493</v>
+        <v>0.1995390541833987</v>
       </c>
       <c r="T77">
-        <v>2.459207462680432</v>
+        <v>2.592261318379472</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.18</v>
+        <v>0.1640417580775056</v>
       </c>
       <c r="W77">
-        <v>0.0738</v>
+        <v>0.1227186699142222</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.506321881908737</v>
+        <v>0.9113431004305866</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1411555621388245</v>
+        <v>0.1421655621388245</v>
       </c>
       <c r="C78">
-        <v>-30.08527270632393</v>
+        <v>-32.1586616656414</v>
       </c>
       <c r="D78">
-        <v>58.13072729367607</v>
+        <v>57.5483383343586</v>
       </c>
       <c r="E78">
-        <v>96.816</v>
+        <v>98.307</v>
       </c>
       <c r="F78">
-        <v>113.316</v>
+        <v>114.807</v>
       </c>
       <c r="G78">
         <v>25.1</v>
@@ -7683,37 +7683,37 @@
         <v>15.16</v>
       </c>
       <c r="M78">
-        <v>16.6347888</v>
+        <v>16.8536676</v>
       </c>
       <c r="N78">
-        <v>-1.474788800000002</v>
+        <v>-1.693667600000001</v>
       </c>
       <c r="O78">
-        <v>-0.2654619840000004</v>
+        <v>-0.3048601680000002</v>
       </c>
       <c r="P78">
-        <v>-1.209326816000002</v>
+        <v>-1.388807432000001</v>
       </c>
       <c r="Q78">
-        <v>6.930673183999998</v>
+        <v>6.751192568</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1995390541833987</v>
+        <v>0.2062233608870247</v>
       </c>
       <c r="T78">
-        <v>2.592261318379472</v>
+        <v>2.704968332222057</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1640417580775056</v>
+        <v>0.1619113456349406</v>
       </c>
       <c r="W78">
-        <v>0.1227186699142222</v>
+        <v>0.1230314144607907</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9113431004305866</v>
+        <v>0.8995074757496699</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1421655621388245</v>
+        <v>0.1431755621388245</v>
       </c>
       <c r="C79">
-        <v>-32.1586616656414</v>
+        <v>-34.22049692379019</v>
       </c>
       <c r="D79">
-        <v>57.5483383343586</v>
+        <v>56.9775030762098</v>
       </c>
       <c r="E79">
-        <v>98.307</v>
+        <v>99.798</v>
       </c>
       <c r="F79">
-        <v>114.807</v>
+        <v>116.298</v>
       </c>
       <c r="G79">
         <v>25.1</v>
@@ -7765,37 +7765,37 @@
         <v>15.16</v>
       </c>
       <c r="M79">
-        <v>16.8536676</v>
+        <v>17.0725464</v>
       </c>
       <c r="N79">
-        <v>-1.693667600000001</v>
+        <v>-1.9125464</v>
       </c>
       <c r="O79">
-        <v>-0.3048601680000002</v>
+        <v>-0.344258352</v>
       </c>
       <c r="P79">
-        <v>-1.388807432000001</v>
+        <v>-1.568288048</v>
       </c>
       <c r="Q79">
-        <v>6.751192568</v>
+        <v>6.571711952</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2062233608870247</v>
+        <v>0.2135153318364349</v>
       </c>
       <c r="T79">
-        <v>2.704968332222057</v>
+        <v>2.827921438232151</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1619113456349406</v>
+        <v>0.1598355591524414</v>
       </c>
       <c r="W79">
-        <v>0.1230314144607907</v>
+        <v>0.1233361399164216</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8995074757496699</v>
+        <v>0.8879753286246743</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1431755621388245</v>
+        <v>0.1441855621388246</v>
       </c>
       <c r="C80">
-        <v>-34.22049692379019</v>
+        <v>-36.27111891541078</v>
       </c>
       <c r="D80">
-        <v>56.9775030762098</v>
+        <v>56.41788108458921</v>
       </c>
       <c r="E80">
-        <v>99.798</v>
+        <v>101.289</v>
       </c>
       <c r="F80">
-        <v>116.298</v>
+        <v>117.789</v>
       </c>
       <c r="G80">
         <v>25.1</v>
@@ -7847,37 +7847,37 @@
         <v>15.16</v>
       </c>
       <c r="M80">
-        <v>17.0725464</v>
+        <v>17.2914252</v>
       </c>
       <c r="N80">
-        <v>-1.9125464</v>
+        <v>-2.131425200000002</v>
       </c>
       <c r="O80">
-        <v>-0.344258352</v>
+        <v>-0.3836565360000004</v>
       </c>
       <c r="P80">
-        <v>-1.568288048</v>
+        <v>-1.747768664000002</v>
       </c>
       <c r="Q80">
-        <v>6.571711952</v>
+        <v>6.392231335999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2135153318364349</v>
+        <v>0.2215017762095985</v>
       </c>
       <c r="T80">
-        <v>2.827921438232151</v>
+        <v>2.962584363862254</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1598355591524414</v>
+        <v>0.1578123242264611</v>
       </c>
       <c r="W80">
-        <v>0.1233361399164216</v>
+        <v>0.1236331508035555</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8879753286246743</v>
+        <v>0.8767351345914505</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1441855621388246</v>
+        <v>0.1451955621388245</v>
       </c>
       <c r="C81">
-        <v>-36.27111891541078</v>
+        <v>-38.31085483049779</v>
       </c>
       <c r="D81">
-        <v>56.41788108458921</v>
+        <v>55.86914516950222</v>
       </c>
       <c r="E81">
-        <v>101.289</v>
+        <v>102.78</v>
       </c>
       <c r="F81">
-        <v>117.789</v>
+        <v>119.28</v>
       </c>
       <c r="G81">
         <v>25.1</v>
@@ -7929,37 +7929,37 @@
         <v>15.16</v>
       </c>
       <c r="M81">
-        <v>17.2914252</v>
+        <v>17.510304</v>
       </c>
       <c r="N81">
-        <v>-2.131425200000002</v>
+        <v>-2.350304000000001</v>
       </c>
       <c r="O81">
-        <v>-0.3836565360000004</v>
+        <v>-0.4230547200000002</v>
       </c>
       <c r="P81">
-        <v>-1.747768664000002</v>
+        <v>-1.927249280000001</v>
       </c>
       <c r="Q81">
-        <v>6.392231335999998</v>
+        <v>6.212750719999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2215017762095985</v>
+        <v>0.2302868650200784</v>
       </c>
       <c r="T81">
-        <v>2.962584363862254</v>
+        <v>3.110713582055366</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1578123242264611</v>
+        <v>0.1558396701736303</v>
       </c>
       <c r="W81">
-        <v>0.1236331508035555</v>
+        <v>0.1239227364185111</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8767351345914505</v>
+        <v>0.8657759454090573</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1451955621388245</v>
+        <v>0.1462055621388245</v>
       </c>
       <c r="C82">
-        <v>-38.31085483049779</v>
+        <v>-40.34001925230099</v>
       </c>
       <c r="D82">
-        <v>55.86914516950222</v>
+        <v>55.33098074769901</v>
       </c>
       <c r="E82">
-        <v>102.78</v>
+        <v>104.271</v>
       </c>
       <c r="F82">
-        <v>119.28</v>
+        <v>120.771</v>
       </c>
       <c r="G82">
         <v>25.1</v>
@@ -8011,37 +8011,37 @@
         <v>15.16</v>
       </c>
       <c r="M82">
-        <v>17.510304</v>
+        <v>17.7291828</v>
       </c>
       <c r="N82">
-        <v>-2.350304000000001</v>
+        <v>-2.5691828</v>
       </c>
       <c r="O82">
-        <v>-0.4230547200000002</v>
+        <v>-0.462452904</v>
       </c>
       <c r="P82">
-        <v>-1.927249280000001</v>
+        <v>-2.106729896</v>
       </c>
       <c r="Q82">
-        <v>6.212750719999999</v>
+        <v>6.033270104000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2302868650200784</v>
+        <v>0.2399967000211352</v>
       </c>
       <c r="T82">
-        <v>3.110713582055366</v>
+        <v>3.274435349531965</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1558396701736303</v>
+        <v>0.1539157236282769</v>
       </c>
       <c r="W82">
-        <v>0.1239227364185111</v>
+        <v>0.124205171771369</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8657759454090573</v>
+        <v>0.8550873534904271</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1462055621388245</v>
+        <v>0.1472155621388245</v>
       </c>
       <c r="C83">
-        <v>-40.34001925230099</v>
+        <v>-42.35891475871031</v>
       </c>
       <c r="D83">
-        <v>55.33098074769901</v>
+        <v>54.80308524128969</v>
       </c>
       <c r="E83">
-        <v>104.271</v>
+        <v>105.762</v>
       </c>
       <c r="F83">
-        <v>120.771</v>
+        <v>122.262</v>
       </c>
       <c r="G83">
         <v>25.1</v>
@@ -8093,37 +8093,37 @@
         <v>15.16</v>
       </c>
       <c r="M83">
-        <v>17.7291828</v>
+        <v>17.9480616</v>
       </c>
       <c r="N83">
-        <v>-2.5691828</v>
+        <v>-2.788061600000002</v>
       </c>
       <c r="O83">
-        <v>-0.462452904</v>
+        <v>-0.5018510880000004</v>
       </c>
       <c r="P83">
-        <v>-2.106729896</v>
+        <v>-2.286210512000002</v>
       </c>
       <c r="Q83">
-        <v>6.033270104000001</v>
+        <v>5.853789487999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2399967000211352</v>
+        <v>0.2507854055778649</v>
       </c>
       <c r="T83">
-        <v>3.274435349531965</v>
+        <v>3.456348424505963</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1539157236282769</v>
+        <v>0.1520387026084198</v>
       </c>
       <c r="W83">
-        <v>0.124205171771369</v>
+        <v>0.124480718457084</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8550873534904271</v>
+        <v>0.8446594589356657</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1472155621388245</v>
+        <v>0.1482255621388245</v>
       </c>
       <c r="C84">
-        <v>-42.35891475871031</v>
+        <v>-44.36783248954036</v>
       </c>
       <c r="D84">
-        <v>54.80308524128969</v>
+        <v>54.28516751045964</v>
       </c>
       <c r="E84">
-        <v>105.762</v>
+        <v>107.253</v>
       </c>
       <c r="F84">
-        <v>122.262</v>
+        <v>123.753</v>
       </c>
       <c r="G84">
         <v>25.1</v>
@@ -8175,37 +8175,37 @@
         <v>15.16</v>
       </c>
       <c r="M84">
-        <v>17.9480616</v>
+        <v>18.1669404</v>
       </c>
       <c r="N84">
-        <v>-2.788061600000002</v>
+        <v>-3.006940400000001</v>
       </c>
       <c r="O84">
-        <v>-0.5018510880000004</v>
+        <v>-0.5412492720000002</v>
       </c>
       <c r="P84">
-        <v>-2.286210512000002</v>
+        <v>-2.465691128000001</v>
       </c>
       <c r="Q84">
-        <v>5.853789487999999</v>
+        <v>5.674308871999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2507854055778649</v>
+        <v>0.262843370611857</v>
       </c>
       <c r="T84">
-        <v>3.456348424505963</v>
+        <v>3.659663037712196</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1520387026084198</v>
+        <v>0.150206911010728</v>
       </c>
       <c r="W84">
-        <v>0.124480718457084</v>
+        <v>0.1247496254636251</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8446594589356657</v>
+        <v>0.8344828389484891</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1482255621388245</v>
+        <v>0.1492355621388246</v>
       </c>
       <c r="C85">
-        <v>-44.36783248954036</v>
+        <v>-46.36705268194932</v>
       </c>
       <c r="D85">
-        <v>54.28516751045964</v>
+        <v>53.77694731805069</v>
       </c>
       <c r="E85">
-        <v>107.253</v>
+        <v>108.744</v>
       </c>
       <c r="F85">
-        <v>123.753</v>
+        <v>125.244</v>
       </c>
       <c r="G85">
         <v>25.1</v>
@@ -8257,37 +8257,37 @@
         <v>15.16</v>
       </c>
       <c r="M85">
-        <v>18.1669404</v>
+        <v>18.3858192</v>
       </c>
       <c r="N85">
-        <v>-3.006940400000001</v>
+        <v>-3.225819200000004</v>
       </c>
       <c r="O85">
-        <v>-0.5412492720000002</v>
+        <v>-0.5806474560000007</v>
       </c>
       <c r="P85">
-        <v>-2.465691128000001</v>
+        <v>-2.645171744000003</v>
       </c>
       <c r="Q85">
-        <v>5.674308871999999</v>
+        <v>5.494828255999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.262843370611857</v>
+        <v>0.2764085812750981</v>
       </c>
       <c r="T85">
-        <v>3.659663037712196</v>
+        <v>3.88839197756921</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.150206911010728</v>
+        <v>0.1484187334986955</v>
       </c>
       <c r="W85">
-        <v>0.1247496254636251</v>
+        <v>0.1250121299223915</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8344828389484891</v>
+        <v>0.8245485194371974</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1492355621388246</v>
+        <v>0.1502455621388245</v>
       </c>
       <c r="C86">
-        <v>-46.36705268194929</v>
+        <v>-48.35684517606101</v>
       </c>
       <c r="D86">
-        <v>53.77694731805069</v>
+        <v>53.27815482393897</v>
       </c>
       <c r="E86">
-        <v>108.744</v>
+        <v>110.235</v>
       </c>
       <c r="F86">
-        <v>125.244</v>
+        <v>126.735</v>
       </c>
       <c r="G86">
         <v>25.1</v>
@@ -8339,37 +8339,37 @@
         <v>15.16</v>
       </c>
       <c r="M86">
-        <v>18.3858192</v>
+        <v>18.604698</v>
       </c>
       <c r="N86">
-        <v>-3.2258192</v>
+        <v>-3.444697999999999</v>
       </c>
       <c r="O86">
-        <v>-0.580647456</v>
+        <v>-0.6200456399999997</v>
       </c>
       <c r="P86">
-        <v>-2.645171744</v>
+        <v>-2.824652359999999</v>
       </c>
       <c r="Q86">
-        <v>5.494828256</v>
+        <v>5.315347640000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2764085812750979</v>
+        <v>0.2917824866934378</v>
       </c>
       <c r="T86">
-        <v>3.888391977569207</v>
+        <v>4.147618109407154</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1484187334986956</v>
+        <v>0.1466726307516521</v>
       </c>
       <c r="W86">
-        <v>0.1250121299223915</v>
+        <v>0.1252684578056575</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8245485194371975</v>
+        <v>0.8148479486202894</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1502455621388245</v>
+        <v>0.1512555621388245</v>
       </c>
       <c r="C87">
-        <v>-48.35684517606101</v>
+        <v>-50.33746989270742</v>
       </c>
       <c r="D87">
-        <v>53.27815482393897</v>
+        <v>52.78853010729257</v>
       </c>
       <c r="E87">
-        <v>110.235</v>
+        <v>111.726</v>
       </c>
       <c r="F87">
-        <v>126.735</v>
+        <v>128.226</v>
       </c>
       <c r="G87">
         <v>25.1</v>
@@ -8421,37 +8421,37 @@
         <v>15.16</v>
       </c>
       <c r="M87">
-        <v>18.604698</v>
+        <v>18.8235768</v>
       </c>
       <c r="N87">
-        <v>-3.444697999999999</v>
+        <v>-3.663576800000001</v>
       </c>
       <c r="O87">
-        <v>-0.6200456399999997</v>
+        <v>-0.6594438240000002</v>
       </c>
       <c r="P87">
-        <v>-2.824652359999999</v>
+        <v>-3.004132976000001</v>
       </c>
       <c r="Q87">
-        <v>5.315347640000001</v>
+        <v>5.135867024</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2917824866934378</v>
+        <v>0.3093526643143977</v>
       </c>
       <c r="T87">
-        <v>4.147618109407154</v>
+        <v>4.44387654579338</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1466726307516521</v>
+        <v>0.1449671350452375</v>
       </c>
       <c r="W87">
-        <v>0.1252684578056575</v>
+        <v>0.1255188245753592</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8148479486202894</v>
+        <v>0.8053729724735418</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1512555621388245</v>
+        <v>0.2006588237216095</v>
       </c>
       <c r="C88">
-        <v>-50.33746989270742</v>
+        <v>-68.1990456228496</v>
       </c>
       <c r="D88">
-        <v>52.78853010729257</v>
+        <v>36.41795437715039</v>
       </c>
       <c r="E88">
-        <v>111.726</v>
+        <v>113.217</v>
       </c>
       <c r="F88">
-        <v>128.226</v>
+        <v>129.717</v>
       </c>
       <c r="G88">
         <v>25.1</v>
@@ -8503,45 +8503,45 @@
         <v>15.16</v>
       </c>
       <c r="M88">
-        <v>18.8235768</v>
+        <v>26.0471736</v>
       </c>
       <c r="N88">
-        <v>-3.663576800000001</v>
+        <v>-10.8871736</v>
       </c>
       <c r="O88">
-        <v>-0.6594438240000002</v>
+        <v>-1.959691247999999</v>
       </c>
       <c r="P88">
-        <v>-3.004132976000001</v>
+        <v>-8.927482351999998</v>
       </c>
       <c r="Q88">
-        <v>5.135867024</v>
+        <v>-0.7874823519999978</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3093526643143977</v>
+        <v>0.340497189129236</v>
       </c>
       <c r="T88">
-        <v>4.44387654579338</v>
+        <v>4.969017977068901</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1449671350452375</v>
+        <v>0.1047637660003157</v>
       </c>
       <c r="W88">
-        <v>0.1255188245753592</v>
+        <v>0.1797634357871366</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8053729724735418</v>
+        <v>0.5820209222239761</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2006588237216095</v>
+        <v>0.2022088237216095</v>
       </c>
       <c r="C89">
-        <v>-68.1990456228496</v>
+        <v>-70.04096784223324</v>
       </c>
       <c r="D89">
-        <v>36.41795437715039</v>
+        <v>36.06703215776675</v>
       </c>
       <c r="E89">
-        <v>113.217</v>
+        <v>114.708</v>
       </c>
       <c r="F89">
-        <v>129.717</v>
+        <v>131.208</v>
       </c>
       <c r="G89">
         <v>25.1</v>
@@ -8585,37 +8585,37 @@
         <v>15.16</v>
       </c>
       <c r="M89">
-        <v>26.0471736</v>
+        <v>26.3465664</v>
       </c>
       <c r="N89">
-        <v>-10.8871736</v>
+        <v>-11.1865664</v>
       </c>
       <c r="O89">
-        <v>-1.959691247999999</v>
+        <v>-2.013581952</v>
       </c>
       <c r="P89">
-        <v>-8.927482351999998</v>
+        <v>-9.172984448000001</v>
       </c>
       <c r="Q89">
-        <v>-0.7874823519999978</v>
+        <v>-1.032984448000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.340497189129236</v>
+        <v>0.365055288223339</v>
       </c>
       <c r="T89">
-        <v>4.969017977068901</v>
+        <v>5.383102808491311</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1047637660003157</v>
+        <v>0.103573268659403</v>
       </c>
       <c r="W89">
-        <v>0.1797634357871366</v>
+        <v>0.1800024876531919</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5820209222239761</v>
+        <v>0.5754070481077944</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2022088237216095</v>
+        <v>0.2037588237216095</v>
       </c>
       <c r="C90">
-        <v>-70.04096784223324</v>
+        <v>-71.87619165712611</v>
       </c>
       <c r="D90">
-        <v>36.06703215776675</v>
+        <v>35.72280834287387</v>
       </c>
       <c r="E90">
-        <v>114.708</v>
+        <v>116.199</v>
       </c>
       <c r="F90">
-        <v>131.208</v>
+        <v>132.699</v>
       </c>
       <c r="G90">
         <v>25.1</v>
@@ -8667,37 +8667,37 @@
         <v>15.16</v>
       </c>
       <c r="M90">
-        <v>26.3465664</v>
+        <v>26.6459592</v>
       </c>
       <c r="N90">
-        <v>-11.1865664</v>
+        <v>-11.4859592</v>
       </c>
       <c r="O90">
-        <v>-2.013581952</v>
+        <v>-2.067472655999999</v>
       </c>
       <c r="P90">
-        <v>-9.172984448000001</v>
+        <v>-9.418486543999997</v>
       </c>
       <c r="Q90">
-        <v>-1.032984448000001</v>
+        <v>-1.278486543999996</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.365055288223339</v>
+        <v>0.3940784962436427</v>
       </c>
       <c r="T90">
-        <v>5.383102808491311</v>
+        <v>5.872475791081431</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.103573268659403</v>
+        <v>0.1024095240677243</v>
       </c>
       <c r="W90">
-        <v>0.1800024876531919</v>
+        <v>0.180236167567201</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5754070481077944</v>
+        <v>0.5689418003762463</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2037588237216095</v>
+        <v>0.2053088237216096</v>
       </c>
       <c r="C91">
-        <v>-71.87619165712611</v>
+        <v>-73.70490704315138</v>
       </c>
       <c r="D91">
-        <v>35.72280834287387</v>
+        <v>35.38509295684862</v>
       </c>
       <c r="E91">
-        <v>116.199</v>
+        <v>117.69</v>
       </c>
       <c r="F91">
-        <v>132.699</v>
+        <v>134.19</v>
       </c>
       <c r="G91">
         <v>25.1</v>
@@ -8749,37 +8749,37 @@
         <v>15.16</v>
       </c>
       <c r="M91">
-        <v>26.6459592</v>
+        <v>26.945352</v>
       </c>
       <c r="N91">
-        <v>-11.4859592</v>
+        <v>-11.785352</v>
       </c>
       <c r="O91">
-        <v>-2.067472655999999</v>
+        <v>-2.12136336</v>
       </c>
       <c r="P91">
-        <v>-9.418486543999997</v>
+        <v>-9.663988639999999</v>
       </c>
       <c r="Q91">
-        <v>-1.278486543999996</v>
+        <v>-1.523988639999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3940784962436427</v>
+        <v>0.4289063458680069</v>
       </c>
       <c r="T91">
-        <v>5.872475791081431</v>
+        <v>6.459723370189574</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1024095240677243</v>
+        <v>0.1012716404669718</v>
       </c>
       <c r="W91">
-        <v>0.180236167567201</v>
+        <v>0.1804646545942321</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5689418003762463</v>
+        <v>0.5626202248165101</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2053088237216096</v>
+        <v>0.2068588237216096</v>
       </c>
       <c r="C92">
-        <v>-73.70490704315138</v>
+        <v>-75.5272968592645</v>
       </c>
       <c r="D92">
-        <v>35.38509295684862</v>
+        <v>35.05370314073551</v>
       </c>
       <c r="E92">
-        <v>117.69</v>
+        <v>119.181</v>
       </c>
       <c r="F92">
-        <v>134.19</v>
+        <v>135.681</v>
       </c>
       <c r="G92">
         <v>25.1</v>
@@ -8831,37 +8831,37 @@
         <v>15.16</v>
       </c>
       <c r="M92">
-        <v>26.945352</v>
+        <v>27.2447448</v>
       </c>
       <c r="N92">
-        <v>-11.785352</v>
+        <v>-12.0847448</v>
       </c>
       <c r="O92">
-        <v>-2.12136336</v>
+        <v>-2.175254064</v>
       </c>
       <c r="P92">
-        <v>-9.663988639999999</v>
+        <v>-9.909490736000002</v>
       </c>
       <c r="Q92">
-        <v>-1.523988639999999</v>
+        <v>-1.769490736000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4289063458680069</v>
+        <v>0.4714737176311189</v>
       </c>
       <c r="T92">
-        <v>6.459723370189574</v>
+        <v>7.17747041132175</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1012716404669718</v>
+        <v>0.1001587652970051</v>
       </c>
       <c r="W92">
-        <v>0.1804646545942321</v>
+        <v>0.1806881199283614</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5626202248165101</v>
+        <v>0.5564375849833616</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2068588237216096</v>
+        <v>0.2084088237216095</v>
       </c>
       <c r="C93">
-        <v>-75.5272968592645</v>
+        <v>-77.34353717790765</v>
       </c>
       <c r="D93">
-        <v>35.05370314073551</v>
+        <v>34.72846282209235</v>
       </c>
       <c r="E93">
-        <v>119.181</v>
+        <v>120.672</v>
       </c>
       <c r="F93">
-        <v>135.681</v>
+        <v>137.172</v>
       </c>
       <c r="G93">
         <v>25.1</v>
@@ -8913,37 +8913,37 @@
         <v>15.16</v>
       </c>
       <c r="M93">
-        <v>27.2447448</v>
+        <v>27.5441376</v>
       </c>
       <c r="N93">
-        <v>-12.0847448</v>
+        <v>-12.3841376</v>
       </c>
       <c r="O93">
-        <v>-2.175254064</v>
+        <v>-2.229144768</v>
       </c>
       <c r="P93">
-        <v>-9.909490736000002</v>
+        <v>-10.154992832</v>
       </c>
       <c r="Q93">
-        <v>-1.769490736000002</v>
+        <v>-2.014992831999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4714737176311189</v>
+        <v>0.5246829323350087</v>
       </c>
       <c r="T93">
-        <v>7.17747041132175</v>
+        <v>8.07465421273697</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1001587652970051</v>
+        <v>0.09907008306551592</v>
       </c>
       <c r="W93">
-        <v>0.1806881199283614</v>
+        <v>0.1809067273204444</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5564375849833616</v>
+        <v>0.5503893503639773</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2084088237216095</v>
+        <v>0.2099588237216096</v>
       </c>
       <c r="C94">
-        <v>-77.34353717790765</v>
+        <v>-79.15379759695362</v>
       </c>
       <c r="D94">
-        <v>34.72846282209235</v>
+        <v>34.40920240304639</v>
       </c>
       <c r="E94">
-        <v>120.672</v>
+        <v>122.163</v>
       </c>
       <c r="F94">
-        <v>137.172</v>
+        <v>138.663</v>
       </c>
       <c r="G94">
         <v>25.1</v>
@@ -8995,37 +8995,37 @@
         <v>15.16</v>
       </c>
       <c r="M94">
-        <v>27.5441376</v>
+        <v>27.8435304</v>
       </c>
       <c r="N94">
-        <v>-12.3841376</v>
+        <v>-12.6835304</v>
       </c>
       <c r="O94">
-        <v>-2.229144768</v>
+        <v>-2.283035472</v>
       </c>
       <c r="P94">
-        <v>-10.154992832</v>
+        <v>-10.400494928</v>
       </c>
       <c r="Q94">
-        <v>-2.014992831999999</v>
+        <v>-2.260494928000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5246829323350087</v>
+        <v>0.5930947798114387</v>
       </c>
       <c r="T94">
-        <v>8.07465421273697</v>
+        <v>9.228176243127967</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09907008306551592</v>
+        <v>0.098004813355134</v>
       </c>
       <c r="W94">
-        <v>0.1809067273204444</v>
+        <v>0.1811206334782891</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5503893503639773</v>
+        <v>0.5444711853063</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2099588237216096</v>
+        <v>0.2115088237216095</v>
       </c>
       <c r="C95">
-        <v>-79.15379759695362</v>
+        <v>-80.95824153459972</v>
       </c>
       <c r="D95">
-        <v>34.40920240304639</v>
+        <v>34.09575846540027</v>
       </c>
       <c r="E95">
-        <v>122.163</v>
+        <v>123.654</v>
       </c>
       <c r="F95">
-        <v>138.663</v>
+        <v>140.154</v>
       </c>
       <c r="G95">
         <v>25.1</v>
@@ -9077,37 +9077,37 @@
         <v>15.16</v>
       </c>
       <c r="M95">
-        <v>27.8435304</v>
+        <v>28.1429232</v>
       </c>
       <c r="N95">
-        <v>-12.6835304</v>
+        <v>-12.9829232</v>
       </c>
       <c r="O95">
-        <v>-2.283035472</v>
+        <v>-2.336926176</v>
       </c>
       <c r="P95">
-        <v>-10.400494928</v>
+        <v>-10.645997024</v>
       </c>
       <c r="Q95">
-        <v>-2.260494928000002</v>
+        <v>-2.505997023999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5930947798114387</v>
+        <v>0.6843105764466785</v>
       </c>
       <c r="T95">
-        <v>9.228176243127967</v>
+        <v>10.76620561698263</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.098004813355134</v>
+        <v>0.09696220895773898</v>
       </c>
       <c r="W95">
-        <v>0.1811206334782891</v>
+        <v>0.181329988441286</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5444711853063</v>
+        <v>0.5386789386541054</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2115088237216095</v>
+        <v>0.2130588237216096</v>
       </c>
       <c r="C96">
-        <v>-80.95824153459972</v>
+        <v>-82.75702650828998</v>
       </c>
       <c r="D96">
-        <v>34.09575846540027</v>
+        <v>33.78797349171002</v>
       </c>
       <c r="E96">
-        <v>123.654</v>
+        <v>125.145</v>
       </c>
       <c r="F96">
-        <v>140.154</v>
+        <v>141.645</v>
       </c>
       <c r="G96">
         <v>25.1</v>
@@ -9159,37 +9159,37 @@
         <v>15.16</v>
       </c>
       <c r="M96">
-        <v>28.1429232</v>
+        <v>28.442316</v>
       </c>
       <c r="N96">
-        <v>-12.9829232</v>
+        <v>-13.282316</v>
       </c>
       <c r="O96">
-        <v>-2.336926176</v>
+        <v>-2.39081688</v>
       </c>
       <c r="P96">
-        <v>-10.645997024</v>
+        <v>-10.89149912</v>
       </c>
       <c r="Q96">
-        <v>-2.505997023999999</v>
+        <v>-2.751499120000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6843105764466785</v>
+        <v>0.8120126917360146</v>
       </c>
       <c r="T96">
-        <v>10.76620561698263</v>
+        <v>12.91944674037916</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09696220895773898</v>
+        <v>0.09594155412660486</v>
       </c>
       <c r="W96">
-        <v>0.181329988441286</v>
+        <v>0.1815349359313777</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5386789386541054</v>
+        <v>0.5330086340366937</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2130588237216096</v>
+        <v>0.2146088237216096</v>
       </c>
       <c r="C97">
-        <v>-82.75702650828998</v>
+        <v>-84.55030439866498</v>
       </c>
       <c r="D97">
-        <v>33.78797349171002</v>
+        <v>33.48569560133502</v>
       </c>
       <c r="E97">
-        <v>125.145</v>
+        <v>126.636</v>
       </c>
       <c r="F97">
-        <v>141.645</v>
+        <v>143.136</v>
       </c>
       <c r="G97">
         <v>25.1</v>
@@ -9241,37 +9241,37 @@
         <v>15.16</v>
       </c>
       <c r="M97">
-        <v>28.442316</v>
+        <v>28.7417088</v>
       </c>
       <c r="N97">
-        <v>-13.282316</v>
+        <v>-13.5817088</v>
       </c>
       <c r="O97">
-        <v>-2.39081688</v>
+        <v>-2.444707584</v>
       </c>
       <c r="P97">
-        <v>-10.89149912</v>
+        <v>-11.137001216</v>
       </c>
       <c r="Q97">
-        <v>-2.751499120000002</v>
+        <v>-2.997001216000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8120126917360146</v>
+        <v>1.003565864670019</v>
       </c>
       <c r="T97">
-        <v>12.91944674037916</v>
+        <v>16.14930842547396</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09594155412660486</v>
+        <v>0.09494216293778607</v>
       </c>
       <c r="W97">
-        <v>0.1815349359313777</v>
+        <v>0.1817356136820926</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5330086340366937</v>
+        <v>0.5274564607654781</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2146088237216096</v>
+        <v>0.2161588237216095</v>
       </c>
       <c r="C98">
-        <v>-84.55030439866498</v>
+        <v>-86.33822169946933</v>
       </c>
       <c r="D98">
-        <v>33.48569560133502</v>
+        <v>33.18877830053065</v>
       </c>
       <c r="E98">
-        <v>126.636</v>
+        <v>128.127</v>
       </c>
       <c r="F98">
-        <v>143.136</v>
+        <v>144.627</v>
       </c>
       <c r="G98">
         <v>25.1</v>
@@ -9323,37 +9323,37 @@
         <v>15.16</v>
       </c>
       <c r="M98">
-        <v>28.7417088</v>
+        <v>29.0411016</v>
       </c>
       <c r="N98">
-        <v>-13.5817088</v>
+        <v>-13.8811016</v>
       </c>
       <c r="O98">
-        <v>-2.444707584</v>
+        <v>-2.498598287999999</v>
       </c>
       <c r="P98">
-        <v>-11.137001216</v>
+        <v>-11.382503312</v>
       </c>
       <c r="Q98">
-        <v>-2.997001216000001</v>
+        <v>-3.242503311999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.003565864670016</v>
+        <v>1.322821152893355</v>
       </c>
       <c r="T98">
-        <v>16.14930842547392</v>
+        <v>21.53241123396522</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09494216293778607</v>
+        <v>0.09396337775286046</v>
       </c>
       <c r="W98">
-        <v>0.1817356136820926</v>
+        <v>0.1819321537472256</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5274564607654781</v>
+        <v>0.5220187652936692</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2161588237216095</v>
+        <v>0.2177088237216095</v>
       </c>
       <c r="C99">
-        <v>-86.33822169946933</v>
+        <v>-88.12091975428038</v>
       </c>
       <c r="D99">
-        <v>33.18877830053065</v>
+        <v>32.89708024571961</v>
       </c>
       <c r="E99">
-        <v>128.127</v>
+        <v>129.618</v>
       </c>
       <c r="F99">
-        <v>144.627</v>
+        <v>146.118</v>
       </c>
       <c r="G99">
         <v>25.1</v>
@@ -9405,37 +9405,37 @@
         <v>15.16</v>
       </c>
       <c r="M99">
-        <v>29.0411016</v>
+        <v>29.3404944</v>
       </c>
       <c r="N99">
-        <v>-13.8811016</v>
+        <v>-14.1804944</v>
       </c>
       <c r="O99">
-        <v>-2.498598287999999</v>
+        <v>-2.552488992</v>
       </c>
       <c r="P99">
-        <v>-11.382503312</v>
+        <v>-11.628005408</v>
       </c>
       <c r="Q99">
-        <v>-3.242503311999997</v>
+        <v>-3.488005407999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.322821152893355</v>
+        <v>1.961331729340033</v>
       </c>
       <c r="T99">
-        <v>21.53241123396522</v>
+        <v>32.29861685094784</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09396337775286046</v>
+        <v>0.09300456777579044</v>
       </c>
       <c r="W99">
-        <v>0.1819321537472256</v>
+        <v>0.1821246827906213</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5220187652936692</v>
+        <v>0.5166920431988358</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2177088237216095</v>
+        <v>0.2192588237216095</v>
       </c>
       <c r="C100">
-        <v>-88.12091975428038</v>
+        <v>-89.89853498086174</v>
       </c>
       <c r="D100">
-        <v>32.89708024571961</v>
+        <v>32.61046501913823</v>
       </c>
       <c r="E100">
-        <v>129.618</v>
+        <v>131.109</v>
       </c>
       <c r="F100">
-        <v>146.118</v>
+        <v>147.609</v>
       </c>
       <c r="G100">
         <v>25.1</v>
@@ -9487,37 +9487,37 @@
         <v>15.16</v>
       </c>
       <c r="M100">
-        <v>29.3404944</v>
+        <v>29.6398872</v>
       </c>
       <c r="N100">
-        <v>-14.1804944</v>
+        <v>-14.4798872</v>
       </c>
       <c r="O100">
-        <v>-2.552488992</v>
+        <v>-2.606379695999999</v>
       </c>
       <c r="P100">
-        <v>-11.628005408</v>
+        <v>-11.873507504</v>
       </c>
       <c r="Q100">
-        <v>-3.488005407999999</v>
+        <v>-3.733507503999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.961331729340033</v>
+        <v>3.876863458680065</v>
       </c>
       <c r="T100">
-        <v>32.29861685094784</v>
+        <v>64.59723370189568</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09300456777579044</v>
+        <v>0.09206512769724712</v>
       </c>
       <c r="W100">
-        <v>0.1821246827906213</v>
+        <v>0.1823133223583928</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5166920431988358</v>
+        <v>0.5114729316513729</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2192588237216095</v>
-      </c>
-      <c r="C101">
-        <v>-89.89853498086174</v>
-      </c>
-      <c r="D101">
-        <v>32.61046501913823</v>
-      </c>
-      <c r="E101">
-        <v>131.109</v>
-      </c>
-      <c r="F101">
-        <v>147.609</v>
-      </c>
-      <c r="G101">
-        <v>25.1</v>
-      </c>
-      <c r="H101">
-        <v>132.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.3</v>
-      </c>
-      <c r="K101">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="L101">
-        <v>15.16</v>
-      </c>
-      <c r="M101">
-        <v>29.6398872</v>
-      </c>
-      <c r="N101">
-        <v>-14.4798872</v>
-      </c>
-      <c r="O101">
-        <v>-2.606379695999999</v>
-      </c>
-      <c r="P101">
-        <v>-11.873507504</v>
-      </c>
-      <c r="Q101">
-        <v>-3.733507503999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.876863458680065</v>
-      </c>
-      <c r="T101">
-        <v>64.59723370189568</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09206512769724712</v>
-      </c>
-      <c r="W101">
-        <v>0.1823133223583928</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5114729316513729</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
